--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,238 +534,246 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-21, 2026-02-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>DIMARO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-02-26, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LYON 2 CIUDAD LA SALLE</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LYON CIUDAD LA SALLE</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -773,300 +781,428 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>PARKSIDE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>PUERTA DORADA ARRECIFE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>PUERTA DORADA MARISMA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>PUERTA DORADA NATURA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>RIVERBLUE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SAN LUCAS LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SAN MATEO - LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Fechas_Intermedia</t>
+          <t>RealIntermedia</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Fechas_Semanal</t>
+          <t>RealSemanal</t>
         </is>
       </c>
     </row>
@@ -441,770 +441,892 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2022-11-21, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-21, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-06, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-16, 2024-03-21, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-05, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-02, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-11, 2024-10-17, 2024-10-24, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18, 2026-03-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2022-11-25, 2022-12-01, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-07, 2023-09-13, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-11, 2024-01-19, 2024-01-29, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-18, 2024-03-22, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-17, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-05, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-30, 2024-09-02, 2024-09-06, 2024-09-16, 2024-09-20, 2024-09-28, 2024-10-03, 2024-10-16, 2024-10-18, 2024-10-25, 2025-12-26, 2025-12-29, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-03, 2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMARETTO</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-12-23, 2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>BAVIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
-        </is>
-      </c>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAVIERA</t>
+          <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>2023-08-10, 2023-08-18, 2023-08-25, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-08, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-14, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-07, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-12, 2025-05-21, 2025-05-26, 2025-05-29, 2025-06-04, 2025-06-12, 2025-06-16, 2025-06-25, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-11, 2025-08-20, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-14, 2025-10-20, 2025-10-28, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-03, 2025-12-11, 2025-12-15, 2025-12-22, 2026-01-05, 2026-01-13, 2026-01-19, 2026-01-26, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23, 2026-03-02, 2026-03-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-08-11, 2023-08-24, 2023-08-30, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-05, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-11, 2023-12-18, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-19, 2024-05-02, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-06, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-13, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-09, 2024-10-16, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-09, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-11, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-21, 2025-05-26, 2025-06-04, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-01, 2025-09-03, 2025-09-12, 2025-09-18, 2025-09-24, 2025-10-01, 2025-10-10, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26, 2025-12-03, 2025-12-05, 2025-12-12, 2025-12-17, 2025-12-30, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-30, 2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25, 2026-03-04, 2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
+          <t>2022-11-17, 2022-11-29, 2022-12-02, 2022-12-09, 2022-12-15, 2022-12-21, 2022-12-28, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-09, 2023-02-23, 2023-03-09, 2023-03-23, 2023-04-13, 2023-04-20, 2023-05-04, 2023-05-06, 2023-05-11, 2023-05-18, 2023-06-01, 2023-06-15, 2023-06-29, 2023-07-13, 2023-07-22, 2023-07-27, 2023-08-10, 2023-08-12, 2023-08-24, 2023-09-07, 2023-09-22, 2023-10-06, 2023-10-20, 2023-11-02, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2023-12-26, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2022-11-28, 2022-12-02, 2022-12-09, 2022-12-16, 2022-12-22, 2022-12-29, 2023-01-06, 2023-01-14, 2023-01-21, 2023-01-27, 2023-02-10, 2023-02-25, 2023-03-11, 2023-03-25, 2023-04-15, 2023-04-22, 2023-05-06, 2023-05-12, 2023-05-20, 2023-06-03, 2023-06-17, 2023-07-01, 2023-07-15, 2023-07-24, 2023-07-29, 2023-08-12, 2023-08-19, 2023-08-26, 2023-09-09, 2023-09-23, 2023-10-07, 2023-10-20, 2023-11-07, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BURGOS CASTILLA RESERVADO</t>
+          <t>CADIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2021-12-28, 2021-12-29, 2022-01-06, 2022-01-11, 2022-01-18, 2022-01-25, 2022-02-01, 2022-02-08, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-15, 2022-03-22, 2022-03-30, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-28, 2022-05-07, 2022-05-18, 2022-05-19, 2022-05-24, 2022-06-02, 2022-06-08, 2022-06-17, 2022-06-22, 2022-06-28, 2022-07-05, 2022-07-12, 2022-07-19, 2022-07-26, 2022-08-02, 2022-08-09, 2022-08-16, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-29, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-27, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-04, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2021-12-28, 2021-12-30, 2022-01-07, 2022-01-18, 2022-01-19, 2022-02-02, 2022-02-03, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-22, 2022-03-23, 2022-03-29, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-27, 2022-05-04, 2022-05-11, 2022-05-18, 2022-05-24, 2022-05-25, 2022-06-02, 2022-06-08, 2022-06-21, 2022-06-23, 2022-06-29, 2022-07-05, 2022-07-13, 2022-07-21, 2022-07-27, 2022-08-03, 2022-08-10, 2022-08-17, 2022-08-25, 2022-09-01, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-27, 2022-10-05, 2022-10-12, 2022-10-20, 2022-10-26, 2022-11-02, 2022-11-10, 2022-11-16, 2022-11-24, 2022-12-01, 2022-12-07, 2022-12-14, 2022-12-20, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-16, 2023-06-23, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-11, 2023-08-17, 2023-08-24, 2023-08-30, 2023-09-07, 2023-09-14, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-20, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-18, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-04, 2024-01-17, 2024-01-22, 2024-01-25, 2024-02-05, 2024-02-10, 2024-02-17, 2024-02-26, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-26, 2025-11-27, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C DEL PARQUE TAYRONA APTOS</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-21, 2026-02-26</t>
+          <t>2024-08-12, 2024-08-13, 2024-10-01, 2024-10-15, 2024-10-21, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-08, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-14, 2025-06-25, 2025-07-02, 2025-07-07, 2025-07-14, 2025-07-18, 2025-07-31, 2025-08-04, 2025-08-11, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-08, 2025-10-20, 2025-10-27, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24, 2025-12-01, 2025-12-10, 2025-12-15, 2025-12-22, 2026-01-14, 2026-01-19, 2026-01-27, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-25, 2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-02-13, 2026-02-21, 2026-02-27</t>
+          <t>2024-08-20, 2024-10-15, 2024-10-17, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-07, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-03, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-05, 2025-05-14, 2025-05-21, 2025-05-26, 2025-06-05, 2025-06-11, 2025-06-20, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-18, 2025-07-21, 2025-07-31, 2025-08-08, 2025-08-12, 2025-08-25, 2025-09-02, 2025-09-08, 2025-09-18, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-16, 2025-10-21, 2025-10-30, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28, 2025-12-03, 2025-12-11, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-13, 2026-02-19, 2026-02-26, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
+          <t>2024-10-18, 2024-10-21, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2024-12-18, 2025-01-10, 2025-01-16, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-12, 2025-06-20, 2025-07-03, 2025-07-10, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-19, 2025-09-26, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25, 2025-12-12, 2025-12-22, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-03, 2026-03-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2024-10-21, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-30, 2024-12-07, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-20, 2025-02-07, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-26, 2025-04-01, 2025-04-09, 2025-04-25, 2025-05-06, 2025-05-19, 2025-05-20, 2025-06-05, 2025-06-06, 2025-06-20, 2025-07-03, 2025-07-04, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-25, 2025-09-02, 2025-09-06, 2025-09-15, 2025-09-19, 2025-09-26, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26, 2025-12-13, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIMARO</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2023-09-13, 2023-09-29, 2023-12-28, 2024-01-06, 2024-01-09, 2024-01-19, 2024-01-27, 2024-02-02, 2024-02-10, 2024-02-14, 2024-02-24, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-23, 2024-04-06, 2024-04-12, 2024-04-17, 2024-04-29, 2024-05-03, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-20, 2024-08-23, 2024-09-03, 2024-09-06, 2024-09-18, 2024-09-20, 2024-10-01, 2024-10-09, 2024-10-11, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-09, 2024-12-14, 2024-12-23, 2024-12-27, 2025-01-08, 2025-01-13, 2025-01-20, 2025-01-24, 2025-01-31, 2025-02-08, 2025-02-14, 2025-02-20, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-22, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-16, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-14, 2025-06-21, 2025-07-01, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-16, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-16, 2025-10-24, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-24, 2025-11-29, 2025-12-03, 2025-12-05, 2025-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-30, 2026-02-02, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-09, 2026-02-13, 2026-02-20, 2026-02-26, 2026-03-02, 2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2023-09-29, 2023-12-28, 2024-01-06, 2024-01-12, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-19, 2024-04-06, 2024-04-09, 2024-04-17, 2024-04-22, 2024-04-29, 2024-05-10, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-30, 2024-08-08, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-19, 2024-11-27, 2024-12-06, 2024-12-11, 2024-12-19, 2024-12-27, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-24, 2025-01-31, 2025-02-03, 2025-02-11, 2025-02-18, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-26, 2025-04-03, 2025-04-07, 2025-04-15, 2025-04-23, 2025-05-03, 2025-05-07, 2025-05-13, 2025-05-23, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-17, 2025-06-25, 2025-07-02, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-29, 2025-09-01, 2025-09-12, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-16, 2025-10-24, 2025-10-27, 2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-16, 2025-12-20, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-31, 2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-23, 2026-02-28, 2026-03-02, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-11, 2024-03-19, 2024-04-02, 2024-04-11, 2024-04-12, 2024-04-23, 2024-05-03, 2024-05-07, 2024-05-14, 2024-05-22, 2024-05-28, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-25, 2024-07-29, 2024-07-31, 2024-08-06, 2024-08-15, 2024-08-16, 2024-08-17, 2024-08-25, 2024-08-27, 2024-09-01, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-04, 2024-10-24, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-15, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-26, 2024-12-27, 2025-01-13, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-27, 2025-01-30, 2025-02-10, 2025-02-20, 2025-03-10, 2025-03-17, 2025-03-19, 2025-03-31, 2025-04-01, 2025-04-02, 2025-04-10, 2025-04-21, 2025-04-23, 2025-04-24, 2025-04-28, 2025-05-10, 2025-05-19, 2025-05-21, 2025-05-22, 2025-06-18, 2025-06-19, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-14, 2025-07-17, 2025-07-28, 2025-07-31, 2025-08-04, 2025-08-05, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-02, 2025-09-05, 2025-09-08, 2025-09-20, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2025-11-27, 2026-03-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-12, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-15, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-07, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-07-26, 2024-07-29, 2024-08-01, 2024-08-09, 2024-08-16, 2024-08-17, 2024-08-22, 2024-08-25, 2024-08-30, 2024-09-01, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-28, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-28, 2024-12-05, 2024-12-26, 2024-12-27, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-19, 2025-02-24, 2025-03-11, 2025-03-18, 2025-03-19, 2025-04-01, 2025-04-02, 2025-04-07, 2025-04-10, 2025-04-23, 2025-04-24, 2025-04-30, 2025-05-10, 2025-05-21, 2025-05-22, 2025-06-19, 2025-06-20, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-29, 2025-08-04, 2025-08-05, 2025-08-06, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-04, 2025-09-05, 2025-09-08, 2025-09-22, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2026-03-06, 2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2023-08-14, 2023-08-25, 2025-07-02, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-13, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+          <t>2023-08-25, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>2022-12-28, 2023-01-06, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-16, 2023-06-22, 2023-06-28, 2023-07-06, 2023-07-13, 2023-07-22, 2023-07-26, 2023-07-31, 2023-08-10, 2023-08-16, 2023-08-25, 2023-09-02, 2023-09-07, 2023-09-13, 2023-09-22, 2023-10-02, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-25, 2023-11-01, 2023-11-09, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-11, 2024-01-16, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-14, 2024-02-21, 2024-03-01, 2024-03-08, 2024-03-13, 2024-03-15, 2024-03-22, 2024-04-04, 2024-04-05, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-07, 2024-05-15, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-08, 2024-10-18, 2024-10-22, 2024-10-28, 2024-11-05, 2024-11-14, 2024-11-21, 2024-11-29, 2025-01-03, 2025-01-16, 2025-03-11, 2025-03-20, 2025-03-25, 2025-03-28, 2025-04-10, 2025-04-22, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-22, 2025-05-29, 2025-06-03, 2025-06-12, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-10, 2025-09-16, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2023-01-06, 2023-01-13, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-19, 2023-05-26, 2023-05-31, 2023-06-07, 2023-06-16, 2023-06-26, 2023-06-28, 2023-07-07, 2023-07-13, 2023-07-22, 2023-07-26, 2023-08-09, 2023-08-16, 2023-08-18, 2023-08-28, 2023-09-02, 2023-09-07, 2023-09-16, 2023-09-22, 2023-10-02, 2023-10-06, 2023-10-13, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-11, 2023-11-16, 2023-11-24, 2023-11-30, 2023-12-11, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-01, 2024-03-08, 2024-03-14, 2024-03-22, 2024-04-05, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-23, 2024-05-31, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-09, 2024-10-18, 2024-10-25, 2024-10-30, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2025-01-03, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-22, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-19, 2025-08-26, 2025-09-04, 2025-09-12, 2025-09-19, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-15, 2024-04-22, 2024-04-27, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-05, 2024-10-10, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-16, 2024-11-23, 2024-11-29, 2024-12-06, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-02, 2025-05-10, 2025-05-19, 2025-05-26, 2025-05-30, 2025-06-09, 2025-06-14, 2025-06-19, 2025-06-27, 2025-06-28, 2025-07-04, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-01, 2025-08-09, 2025-08-15, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-25, 2025-10-29, 2025-11-07, 2025-11-10, 2025-11-21, 2025-11-22, 2025-11-26, 2025-12-06, 2025-12-13, 2025-12-20, 2025-12-22, 2026-01-08, 2026-01-13, 2026-01-22, 2026-02-26, 2026-03-03, 2026-03-05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-26, 2024-10-05, 2024-10-11, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-17, 2024-11-23, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-04, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-02, 2025-06-09, 2025-06-16, 2025-06-19, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-14, 2025-12-20, 2025-12-22, 2026-01-13, 2026-02-10, 2026-02-28, 2026-03-03, 2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>LA CRUZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-20, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-25, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-23, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-25, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-07, 2025-07-10, 2025-07-25, 2025-08-13, 2025-09-04, 2025-10-17, 2025-10-24, 2025-11-13, 2025-11-21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-22, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-27, 2024-05-31, 2024-06-07, 2024-06-13, 2024-06-26, 2024-06-28, 2024-07-04, 2024-07-18, 2024-07-19, 2024-07-25, 2024-08-05, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-23, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-22, 2025-02-27, 2025-03-14, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-25, 2025-05-02, 2025-05-13, 2025-05-19, 2025-05-23, 2025-06-06, 2025-06-14, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-07, 2025-07-25, 2025-08-13, 2025-10-17, 2025-10-18, 2025-10-24, 2025-11-21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2023-11-14, 2023-11-16, 2023-11-21, 2023-11-28, 2023-12-07, 2023-12-15, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-08, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-12, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-25, 2024-08-01, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-09, 2024-09-13, 2024-09-24, 2024-09-26, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-14, 2024-12-27, 2025-01-24, 2025-02-02, 2025-02-08, 2025-02-13, 2025-02-22, 2025-03-01, 2025-03-03, 2025-03-14, 2025-03-17, 2025-03-30, 2025-04-06, 2025-04-13, 2025-04-23, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-01, 2025-06-05, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-21, 2025-07-27, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-29, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-26, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2023-11-14, 2023-11-17, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-14, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-01, 2024-03-09, 2024-03-15, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-20, 2024-04-27, 2024-05-05, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-26, 2024-08-31, 2024-09-09, 2024-09-14, 2024-09-24, 2024-09-27, 2024-10-05, 2024-10-11, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-12-01, 2024-12-07, 2024-12-14, 2025-01-18, 2025-01-25, 2025-02-03, 2025-02-08, 2025-02-15, 2025-02-23, 2025-03-01, 2025-03-09, 2025-03-14, 2025-03-22, 2025-03-30, 2025-04-08, 2025-04-13, 2025-04-26, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-02, 2025-06-08, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-13, 2025-07-21, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-30, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-27, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-28</t>
+          <t>2024-05-29, 2024-06-04, 2024-06-11, 2024-06-26, 2024-07-06, 2024-07-12, 2024-07-17, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-08, 2025-01-14, 2025-01-21, 2025-01-29, 2025-02-04, 2025-02-11, 2025-02-20, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-03, 2025-07-09, 2025-07-16, 2025-07-23, 2025-08-01, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-12, 2025-09-17, 2025-09-24, 2025-10-02, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-19, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02-26, 2026-02-28</t>
+          <t>2024-06-04, 2024-06-11, 2024-06-22, 2024-06-27, 2024-07-06, 2024-07-12, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-07, 2025-03-17, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-04-30, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-12, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2025-07-02, 2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-14, 2025-08-20, 2025-09-03, 2025-09-16, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-17, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-12-01, 2025-12-04, 2025-12-12, 2026-01-07, 2026-01-10, 2026-01-16, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2022-11-29, 2022-12-16, 2022-12-20, 2022-12-28, 2023-01-13, 2023-01-18, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-04, 2023-07-11, 2023-07-19, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-16, 2023-08-22, 2023-08-29, 2023-09-05, 2024-10-16, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-05, 2025-02-10, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-27, 2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2022-12-12, 2022-12-19, 2022-12-26, 2022-12-29, 2023-01-13, 2023-01-19, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-11, 2023-04-13, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-15, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-10, 2023-08-16, 2023-08-23, 2023-08-31, 2023-09-05, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-10, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-22, 2025-05-29, 2025-06-07, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LINZ E1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2023-10-23, 2023-11-10, 2023-12-07, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-05, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-19, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-07, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-17, 2025-03-19, 2025-03-25, 2025-04-02, 2025-04-03, 2025-04-23, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-21, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2023-11-10, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-29, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-01, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-07, 2024-11-15, 2024-11-21, 2024-11-28, 2024-12-03, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-21, 2025-01-30, 2025-02-05, 2025-02-11, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-17, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-26, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-21, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-20, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-08, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-19, 2023-08-29, 2023-08-30, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-22, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-09, 2024-09-16, 2024-09-24, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-05, 2024-12-09, 2024-12-16, 2024-12-27, 2025-01-13, 2025-01-20, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-05, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-04, 2025-03-06, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-01, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-06, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-10, 2025-06-17, 2025-06-26, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-02, 2025-11-19, 2026-02-11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-29, 2022-12-05, 2022-12-13, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-27, 2023-02-28, 2023-03-13, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-11, 2023-04-21, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-26, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-08, 2024-02-16, 2024-02-22, 2024-03-01, 2024-03-06, 2024-03-13, 2024-03-21, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-30, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-05, 2024-12-11, 2024-12-19, 2025-01-10, 2025-01-17, 2025-01-21, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-07, 2025-02-12, 2025-02-19, 2025-02-27, 2025-03-04, 2025-03-06, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-21, 2025-05-28, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-26, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-23, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-09, 2025-11-20, 2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-07, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-28, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-14, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-23, 2025-04-30, 2025-05-02, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-11, 2025-08-26, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-17, 2025-11-19, 2025-11-26, 2025-12-05, 2025-12-10, 2025-12-22, 2025-12-27, 2025-12-29, 2026-01-07, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-14, 2026-02-16, 2026-02-18, 2026-02-20, 2026-02-24, 2026-02-25, 2026-03-04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-09-02, 2023-09-07, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-19, 2023-10-27, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-02, 2024-01-05, 2024-01-12, 2024-01-19, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-30, 2024-05-02, 2024-05-11, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-20, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-23, 2025-04-24, 2025-05-02, 2025-05-07, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-26, 2025-08-28, 2025-09-10, 2025-09-11, 2025-09-23, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-20, 2025-10-24, 2025-10-30, 2025-11-04, 2025-11-17, 2025-11-20, 2025-12-05, 2025-12-13, 2025-12-22, 2025-12-27, 2026-01-07, 2026-01-13, 2026-01-21, 2026-01-27, 2026-01-30, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25, 2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-08-31, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-28, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-18, 2023-01-24, 2023-01-30, 2023-02-08, 2023-02-16, 2023-02-22, 2023-03-03, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-28, 2023-09-06, 2023-09-11, 2023-09-18, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-22, 2023-10-30, 2023-11-06, 2023-11-14, 2023-11-23, 2023-11-27, 2023-12-05, 2023-12-11, 2023-12-27, 2024-01-09, 2024-01-15, 2024-01-24, 2024-01-29, 2024-02-05, 2024-02-14, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-13, 2024-04-17, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-04, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-29, 2024-08-05, 2024-08-09, 2024-08-10, 2024-08-12, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-24, 2024-08-29, 2024-09-02, 2024-09-06, 2024-09-07, 2024-09-14, 2024-09-20, 2024-09-23, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-02-24, 2025-03-05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
+          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-09-02, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-19, 2023-01-31, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-07, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-07-21, 2023-08-02, 2023-08-09, 2023-08-18, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-16, 2023-09-20, 2023-09-29, 2023-10-06, 2023-10-17, 2023-10-18, 2023-10-30, 2023-11-01, 2023-11-08, 2023-11-17, 2023-11-27, 2023-11-30, 2023-12-08, 2023-12-14, 2023-12-28, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-15, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-04, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-18, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-27, 2024-08-01, 2024-08-05, 2024-08-08, 2024-08-09, 2024-08-10, 2024-08-13, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-28, 2024-08-29, 2024-09-03, 2024-09-06, 2024-09-12, 2024-09-20, 2024-10-02, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-03-05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LYON 2 CIUDAD LA SALLE</t>
+          <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>2022-08-03, 2022-08-09, 2022-08-18, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-16, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-15, 2023-02-22, 2023-02-28, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-10, 2023-07-19, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-24, 2023-12-04, 2023-12-11, 2023-12-18, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-07, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-04, 2024-04-08, 2024-04-15, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-22, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-12, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-13, 2024-09-25, 2024-10-29, 2025-02-24, 2025-03-05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2022-08-05, 2022-08-09, 2022-08-18, 2022-08-23, 2022-09-01, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-18, 2023-01-26, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-03, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-08, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-16, 2023-10-20, 2023-10-26, 2023-11-02, 2023-11-13, 2023-11-15, 2023-11-29, 2023-12-07, 2023-12-18, 2023-12-20, 2023-12-28, 2024-01-03, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-17, 2024-07-23, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-25, 2024-11-01, 2025-02-24, 2025-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LYON CIUDAD LA SALLE</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>2025-05-28, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-06-04, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-09-02, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-10, 2025-10-17, 2025-10-23, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27, 2025-12-05, 2025-12-11, 2025-12-18, 2025-12-26, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2022-09-02, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-12, 2022-12-19, 2022-12-26, 2023-01-02, 2023-01-10, 2023-01-16, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-22, 2023-02-23, 2023-03-07, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-13, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-02, 2025-07-08, 2025-07-17, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-02, 2025-09-09, 2025-09-24, 2025-09-30, 2025-10-06, 2025-10-07, 2025-10-14, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-09, 2025-12-15, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2022-09-08, 2022-09-15, 2022-09-21, 2022-09-28, 2022-10-12, 2022-10-19, 2022-10-29, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-25, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-26, 2022-12-27, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-26, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-31, 2023-06-01, 2023-06-09, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-21, 2023-12-27, 2024-01-03, 2024-01-12, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-04, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-06, 2024-06-12, 2024-06-18, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-12, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-09, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-30, 2025-09-04, 2025-09-16, 2025-09-25, 2025-10-02, 2025-10-06, 2025-10-10, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-24, 2025-10-30, 2025-11-07, 2025-11-11, 2025-11-13, 2025-11-18, 2025-11-21, 2025-11-26, 2025-11-28, 2025-12-03, 2025-12-05, 2025-12-11, 2025-12-19, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04, 2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2022-11-22, 2022-11-30, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-28, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-05, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-12, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-27, 2024-12-03, 2024-12-10, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2022-11-26, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-12, 2023-01-18, 2023-01-25, 2023-02-03, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-12, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-22, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-20, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-13, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2023-08-14, 2023-08-15, 2023-08-25, 2023-08-27, 2023-08-30, 2023-09-06, 2023-10-05, 2023-10-19, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2024-12-30, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-13, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-27, 2025-09-02, 2025-09-09, 2025-09-17, 2025-09-24, 2025-09-29, 2025-10-02, 2025-10-07, 2025-10-14, 2025-10-15, 2025-10-17, 2025-10-21, 2025-10-24, 2025-10-27, 2025-10-28, 2025-11-05, 2025-11-07, 2025-11-11, 2025-11-12, 2025-11-19, 2025-11-25, 2025-11-28, 2025-12-03, 2025-12-10, 2025-12-27, 2026-01-06, 2026-01-26, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+          <t>2023-08-14, 2023-08-25, 2023-08-28, 2023-08-30, 2023-09-06, 2023-10-13, 2023-10-20, 2023-10-31, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-15, 2023-12-21, 2024-01-04, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-03, 2024-02-15, 2024-02-19, 2024-02-24, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-22, 2024-04-24, 2024-05-02, 2024-05-14, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-18, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-09, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-05, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-27, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-15, 2025-10-17, 2025-10-24, 2025-10-27, 2025-10-31, 2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-27, 2025-11-28, 2025-12-03, 2025-12-04, 2025-12-12, 2025-12-27, 2026-01-09, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PARKSIDE</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-23</t>
+          <t>2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-29, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-04, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-10, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-12, 2025-08-19, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
+          <t>2022-11-24, 2022-12-01, 2022-12-09, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-03, 2023-03-10, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-10, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-03, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-17, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-15, 2025-07-21, 2025-07-28, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-03, 2025-09-08, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+          <t>2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-03, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-17, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-05, 2023-09-11, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-08, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-03, 2024-07-08, 2024-07-10, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-08, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-13, 2025-05-29, 2025-06-19, 2025-07-07, 2025-07-14, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-12, 2025-08-29, 2025-09-11, 2025-09-16, 2025-09-22, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
+          <t>2022-12-26, 2022-12-29, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-18, 2023-07-25, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-20, 2023-09-26, 2023-10-03, 2023-10-13, 2023-10-17, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-12, 2023-12-19, 2023-12-27, 2024-01-05, 2024-01-10, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-12, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-10, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-23, 2024-08-29, 2024-09-03, 2024-09-11, 2024-09-17, 2024-09-24, 2024-10-02, 2024-10-09, 2024-10-17, 2024-10-25, 2024-10-30, 2024-11-26, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-14, 2025-05-30, 2025-07-07, 2025-07-14, 2025-07-28, 2025-07-31, 2025-08-06, 2025-08-15, 2025-09-05, 2025-09-11, 2025-09-16, 2025-09-23, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2022-11-17, 2022-12-01, 2022-12-15, 2023-02-03, 2023-02-10, 2023-02-16, 2023-02-23, 2023-03-01, 2023-03-07, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-17, 2023-08-25, 2023-08-31, 2023-09-08, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2024-12-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+          <t>2022-11-24, 2022-12-01, 2023-02-02, 2023-02-03, 2023-02-13, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-11, 2023-03-17, 2023-03-25, 2023-03-31, 2023-04-14, 2023-04-27, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-08-02, 2023-08-05, 2023-08-11, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-25, 2023-10-27, 2023-11-17, 2023-11-24, 2023-12-06, 2024-02-02</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2023-03-14, 2023-03-21, 2023-03-28, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-05, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-04, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-23, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-20, 2023-11-27, 2023-12-04, 2023-12-11, 2023-12-18, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-07, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-23, 2024-09-02, 2024-09-10, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-25, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-28, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-23, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-10-01, 2025-10-09, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-09, 2025-12-18, 2026-01-14, 2026-01-20, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-13, 2023-04-26, 2023-05-04, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-09, 2024-04-17, 2024-04-24, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-21, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>2022-12-07, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-11, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-18, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-04, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-05, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-10, 2024-03-17, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-15, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-26, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-31, 2024-11-05, 2024-11-11, 2024-11-16, 2024-11-28, 2024-12-03, 2024-12-10, 2025-01-09, 2025-01-14, 2025-01-21, 2025-01-30, 2025-02-07, 2025-02-14, 2025-02-22, 2025-03-01, 2025-03-18, 2025-04-12, 2025-04-24, 2025-06-19, 2025-12-26, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-13, 2026-01-20, 2026-01-21, 2026-01-22, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-02-17, 2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2022-12-09, 2022-12-16, 2022-12-22, 2022-12-30, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-29, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-20, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-16, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-16, 2023-12-21, 2023-12-28, 2024-01-05, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-03, 2024-03-08, 2024-03-16, 2024-04-04, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-27, 2024-05-03, 2024-05-11, 2024-05-18, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-01, 2024-08-10, 2024-08-15, 2024-08-24, 2024-08-26, 2024-08-30, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-09, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-21, 2024-11-30, 2024-12-07, 2024-12-13, 2025-01-10, 2025-01-20, 2025-01-25, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-24, 2025-03-01, 2025-03-26, 2025-04-24, 2025-06-04, 2025-07-04, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-19, 2026-01-20, 2026-01-21, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-30, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PUERTA DORADA ARRECIFE</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2023-08-14, 2023-08-25, 2023-08-27, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-12, 2024-03-21, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-22, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-05, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-15, 2025-01-21, 2025-01-28, 2025-02-06, 2025-02-11, 2025-02-18, 2025-02-26, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-28, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-04, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2025-12-30, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-19, 2026-02-24, 2026-03-03, 2026-03-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2023-08-25, 2024-01-31, 2024-02-16, 2024-02-24, 2024-03-01, 2024-03-09, 2024-03-16, 2024-03-23, 2024-03-27, 2024-04-04, 2024-04-13, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-10, 2024-05-18, 2024-05-25, 2024-06-01, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-29, 2024-07-06, 2024-07-12, 2024-07-19, 2024-07-27, 2024-08-06, 2024-08-10, 2024-08-16, 2024-08-25, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-25, 2024-10-04, 2024-10-12, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-27, 2024-12-07, 2024-12-12, 2024-12-18, 2025-01-09, 2025-01-17, 2025-01-22, 2025-01-29, 2025-02-08, 2025-02-13, 2025-02-21, 2025-02-27, 2025-03-07, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-11, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-02, 2025-07-11, 2025-07-17, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-15, 2025-08-21, 2025-08-29, 2025-09-03, 2025-09-11, 2025-09-19, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-25, 2025-10-31, 2025-11-06, 2025-11-11, 2025-11-21, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-17, 2025-12-27, 2026-01-03, 2026-01-09, 2026-01-16, 2026-01-26, 2026-01-29, 2026-02-07, 2026-02-12, 2026-02-19, 2026-02-24, 2026-03-04, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
+          <t>2023-08-14, 2025-12-22, 2025-12-26, 2026-01-02, 2026-01-07, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25, 2026-03-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
+          <t>2025-12-26, 2026-01-02, 2026-01-08, 2026-01-16, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PUERTA DORADA MARISMA</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
+          <t>2025-10-31, 2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-26, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2025-12-27, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PUERTA DORADA NATURA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2023-06-07, 2023-06-14, 2023-06-21, 2023-06-29, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-09, 2023-08-16, 2023-08-24, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-16, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-02-01, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-30, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-28, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-20, 2025-01-08, 2025-01-15, 2025-01-22, 2025-01-30, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-05, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-25, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27, 2025-12-04, 2025-12-10, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-27</t>
+          <t>2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-28, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-20, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-05-03, 2025-05-08, 2025-05-15, 2025-05-24, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-12, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
+          <t>2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-10, 2023-11-17, 2024-08-06, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-23, 2024-12-27, 2025-01-10, 2025-01-17, 2025-02-07, 2025-02-14, 2025-02-28, 2025-03-07, 2025-03-17, 2025-03-21, 2025-04-09, 2025-05-17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
+          <t>2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-14, 2023-11-17, 2024-08-16, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-20, 2024-09-25, 2024-10-03, 2024-10-08, 2024-10-17, 2024-10-25, 2024-10-29, 2024-11-06, 2024-11-13, 2024-12-04, 2024-12-09, 2024-12-18, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-02-12, 2025-02-17, 2025-03-05, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RIVERBLUE</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2024-06-12, 2024-06-19, 2024-06-24, 2024-07-04, 2024-07-11, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-05, 2024-12-11, 2024-12-19, 2024-12-26, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-03, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-03, 2025-09-11, 2025-09-18, 2025-09-24, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-27, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-26, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-28, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
+          <t>2024-06-12, 2024-06-21, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-17, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-29, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-21, 2025-11-27, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2024-12-12, 2024-12-21, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-22, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29, 2025-12-05, 2025-12-11, 2025-12-19, 2026-01-17, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-14, 2026-02-20, 2026-02-24, 2026-03-05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-01-07, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-31, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-08, 2025-03-14, 2025-03-22, 2025-03-27, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-06, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29, 2025-12-06, 2025-12-12, 2026-01-17, 2026-01-23, 2026-01-31, 2026-02-06, 2026-02-14, 2026-02-21, 2026-02-28, 2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>ZURI - ZENTRAL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2023-08-14, 2024-08-20, 2025-01-15, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-15, 2025-07-23, 2025-07-25, 2025-08-02, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-24, 2025-10-28, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-20, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2024-02-22, 2025-01-15, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-02, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-24, 2025-10-29, 2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27, 2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2023-09-07, 2023-09-12, 2023-09-19, 2023-09-25, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-20, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-25, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-18, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-16, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-29, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2025-12-27, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-03, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2023-09-07, 2023-09-12, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-21, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-11, 2024-10-16, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-11, 2025-01-10, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-28, 2025-03-07, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-30, 2025-06-07, 2025-06-13, 2025-06-26, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-22, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2025-12-27, 2026-01-14, 2026-01-24, 2026-02-02, 2026-02-03, 2026-02-09, 2026-02-18, 2026-02-21, 2026-03-03, 2026-03-06, 2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2023-08-04, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-25, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-18, 2026-02-26, 2026-03-05, 2026-03-12, 2026-03-19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2023-08-31, 2024-10-25, 2024-11-02, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-03-06, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-27, 2025-04-04, 2025-04-12, 2025-04-26, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-31, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-24, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26, 2026-03-05, 2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2023-08-01, 2023-08-29, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25, 2025-12-02, 2026-01-19, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-11, 2026-02-18, 2026-02-24, 2026-03-03, 2026-03-10, 2026-03-17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+          <t>2025-02-05, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-10, 2025-04-24, 2025-05-07, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-19, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26, 2026-01-13, 2026-01-19, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-21, 2026-02-25, 2026-03-04, 2026-03-11, 2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-13, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-29, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-20, 2026-01-15, 2026-01-22, 2026-02-21, 2026-02-26, 2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+          <t>2023-02-02, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-18, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-20, 2026-01-16, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ZURI - ZENTRAL</t>
+          <t>DIMARO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2022-11-30, 2022-12-07, 2022-12-13, 2022-12-21, 2022-12-30, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-04, 2023-09-13, 2023-09-21, 2023-09-27, 2023-10-04, 2023-10-10, 2023-10-18, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-10, 2024-01-25, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-06, 2024-03-12, 2024-03-19, 2024-04-03, 2024-04-09, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-26, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-24, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-08-30, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-29, 2024-11-05, 2024-11-13, 2024-11-19, 2024-11-26, 2024-12-02, 2024-12-10, 2024-12-17, 2025-01-07, 2025-01-15, 2025-01-22, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-05, 2025-03-10, 2025-03-18, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-07, 2025-05-13, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-13, 2025-06-18, 2025-06-25, 2025-07-01, 2025-07-09, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-08, 2025-09-16, 2025-09-25, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-17, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2022-12-02, 2022-12-07, 2022-12-14, 2022-12-22, 2022-12-30, 2023-01-11, 2023-01-20, 2023-01-25, 2023-02-02, 2023-02-08, 2023-02-17, 2023-02-22, 2023-03-01, 2023-03-09, 2023-03-16, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-12, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-13, 2023-07-19, 2023-07-26, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-28, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-13, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-05, 2024-09-11, 2024-09-18, 2024-09-24, 2024-10-08, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-06, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-28, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-26, 2025-03-10, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-05, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-01, 2025-07-10, 2025-07-16, 2025-07-25, 2025-08-02, 2025-08-11, 2025-08-13, 2025-08-21, 2025-08-27, 2025-09-04, 2025-09-10, 2025-09-17, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-20, 2025-10-24, 2025-10-28, 2025-11-05, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-19, 2026-01-22, 2026-01-28, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GENOVA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2024-01-12, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-02-29, 2024-03-05, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-07, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-13, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-28, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-27, 2025-09-05, 2025-09-11, 2025-09-26, 2025-10-09, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-16, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-13</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2024-01-26, 2024-01-30, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-26, 2025-10-11, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PARKSIDE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-10-01, 2025-10-15, 2025-10-29, 2025-11-12, 2025-11-19, 2025-12-03, 2026-01-07, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-02, 2026-03-09, 2026-03-18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025-10-01, 2025-10-29, 2025-11-12, 2025-11-14, 2025-12-03, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-09, 2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA ARRECIFE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2023-02-10, 2023-02-16, 2023-02-24, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-23, 2023-03-31, 2023-04-10, 2023-04-15, 2023-04-21, 2023-04-28, 2023-05-06, 2023-05-12, 2023-05-20, 2023-05-26, 2023-06-03, 2023-06-09, 2023-06-16, 2023-06-24, 2023-06-30, 2023-07-07, 2023-08-08, 2023-08-11, 2023-08-22, 2023-08-26, 2023-09-01, 2023-09-09, 2023-09-16, 2023-09-23, 2023-09-29, 2023-10-09, 2023-10-17, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-11, 2023-11-17, 2023-11-27, 2023-12-02, 2023-12-07, 2023-12-18, 2023-12-22, 2023-12-29, 2024-01-10, 2024-01-13, 2024-01-19, 2024-01-27, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-24, 2024-03-05, 2024-03-12, 2024-03-18, 2024-03-22, 2024-04-02, 2024-04-09, 2024-04-13, 2024-04-20, 2024-04-26, 2024-05-02, 2024-05-11, 2024-05-18, 2024-05-25, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-22, 2024-06-29, 2024-07-09, 2024-07-11, 2024-07-19, 2024-07-27, 2024-08-01, 2024-08-08, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-04, 2025-04-11, 2025-04-24, 2025-04-29, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-25, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-17, 2025-10-23, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-11, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-09, 2025-12-19, 2025-12-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2023-02-13, 2023-02-16, 2023-02-24, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-22, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-17, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-29, 2023-06-03, 2023-06-05, 2023-06-13, 2023-06-20, 2023-06-26, 2023-07-04, 2023-07-13, 2023-08-09, 2023-08-14, 2023-08-24, 2023-08-28, 2023-09-04, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-10, 2023-10-19, 2023-10-24, 2023-10-31, 2023-11-08, 2023-11-16, 2023-11-20, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-10, 2024-01-16, 2024-01-24, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-26, 2024-04-30, 2024-05-07, 2024-05-18, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-22, 2024-06-25, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-10, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-25, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-09, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-28, 2025-07-05, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-12, 2025-12-20, 2026-01-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA MARISMA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2023-08-01, 2023-08-28, 2023-10-03, 2023-11-29, 2024-01-25, 2024-01-31, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-04, 2024-10-10, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2024-12-27, 2025-01-03, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2026-01-16, 2026-01-19, 2026-01-20, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-13</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2023-08-28, 2023-10-03, 2024-01-25, 2024-01-31, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-03-02, 2024-03-12, 2024-03-15, 2024-03-20, 2024-03-22, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-12, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2024-12-28, 2025-01-04, 2025-01-11, 2025-01-18, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-03-05, 2025-03-08, 2025-03-15, 2025-03-22, 2025-03-29, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-13, 2026-01-17, 2026-01-20, 2026-01-24, 2026-01-31, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA NATURA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2023-07-31, 2023-08-29, 2023-10-11, 2023-11-30, 2024-04-25, 2024-05-23, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-15, 2025-03-20, 2025-03-29, 2025-04-07, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-22, 2025-05-30, 2025-06-02, 2025-06-12, 2025-06-21, 2025-06-28, 2025-07-03, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-08, 2025-08-14, 2025-08-23, 2025-08-28, 2025-09-06, 2025-09-11, 2025-09-19, 2025-09-30, 2025-10-04, 2025-10-11, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-11-29, 2025-12-13, 2026-01-15, 2026-01-16, 2026-01-23, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-13, 2026-03-19</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2023-10-11, 2024-04-25, 2024-05-23, 2024-08-28, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-11, 2024-10-18, 2024-10-27, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-16, 2025-02-22, 2025-03-08, 2025-03-18, 2025-03-22, 2025-03-29, 2025-04-07, 2025-04-13, 2025-04-30, 2025-05-08, 2025-05-12, 2025-05-21, 2025-05-29, 2025-06-01, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-12, 2025-09-19, 2025-10-01, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-15, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RIVERBLUE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-08-15, 2025-08-22, 2025-09-02, 2025-09-05, 2025-09-13, 2025-09-19, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-23, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-14, 2025-11-21, 2025-12-04, 2025-12-09, 2025-12-12, 2025-12-19, 2026-01-09, 2026-01-19, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28, 2026-03-07, 2026-03-13</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022-11-21, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-21, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-06, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-16, 2024-03-21, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-05, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-02, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-11, 2024-10-17, 2024-10-24, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18, 2026-03-03</t>
+          <t>2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2022-11-25, 2022-12-01, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-07, 2023-09-13, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-11, 2024-01-19, 2024-01-29, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-18, 2024-03-22, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-11, 2024-05-17, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-05, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-30, 2024-09-02, 2024-09-06, 2024-09-16, 2024-09-20, 2024-09-28, 2024-10-03, 2024-10-16, 2024-10-18, 2024-10-25, 2025-12-26, 2025-12-29, 2026-01-02, 2026-01-05, 2026-01-06, 2026-01-08, 2026-01-13, 2026-01-29, 2026-01-30, 2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-12-23, 2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-12-26, 2026-01-06, 2026-01-23, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
     </row>
@@ -473,11 +473,7 @@
           <t>BAVIERA</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -488,12 +484,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-08-10, 2023-08-18, 2023-08-25, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-08, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-14, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-07, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-12, 2025-05-21, 2025-05-26, 2025-05-29, 2025-06-04, 2025-06-12, 2025-06-16, 2025-06-25, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-11, 2025-08-20, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-14, 2025-10-20, 2025-10-28, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-03, 2025-12-11, 2025-12-15, 2025-12-22, 2026-01-05, 2026-01-13, 2026-01-19, 2026-01-26, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2023-08-11, 2023-08-24, 2023-08-30, 2023-08-31, 2023-09-01, 2023-09-04, 2023-09-05, 2023-09-18, 2023-10-04, 2023-10-20, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-11, 2023-12-18, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-12, 2024-04-19, 2024-05-02, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-06, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-09, 2024-07-12, 2024-07-13, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-09, 2024-10-16, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-09, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-11, 2025-03-17, 2025-03-28, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-21, 2025-05-26, 2025-06-04, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-01, 2025-09-03, 2025-09-12, 2025-09-18, 2025-09-24, 2025-10-01, 2025-10-10, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26, 2025-12-03, 2025-12-05, 2025-12-12, 2025-12-17, 2025-12-30, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-30, 2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25, 2026-03-04, 2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
     </row>
@@ -505,12 +501,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2022-11-17, 2022-11-29, 2022-12-02, 2022-12-09, 2022-12-15, 2022-12-21, 2022-12-28, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-09, 2023-02-23, 2023-03-09, 2023-03-23, 2023-04-13, 2023-04-20, 2023-05-04, 2023-05-06, 2023-05-11, 2023-05-18, 2023-06-01, 2023-06-15, 2023-06-29, 2023-07-13, 2023-07-22, 2023-07-27, 2023-08-10, 2023-08-12, 2023-08-24, 2023-09-07, 2023-09-22, 2023-10-06, 2023-10-20, 2023-11-02, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2023-12-26, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-10, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2022-11-28, 2022-12-02, 2022-12-09, 2022-12-16, 2022-12-22, 2022-12-29, 2023-01-06, 2023-01-14, 2023-01-21, 2023-01-27, 2023-02-10, 2023-02-25, 2023-03-11, 2023-03-25, 2023-04-15, 2023-04-22, 2023-05-06, 2023-05-12, 2023-05-20, 2023-06-03, 2023-06-17, 2023-07-01, 2023-07-15, 2023-07-24, 2023-07-29, 2023-08-12, 2023-08-19, 2023-08-26, 2023-09-09, 2023-09-23, 2023-10-07, 2023-10-20, 2023-11-07, 2023-11-14, 2023-11-17, 2023-11-30, 2023-12-07, 2023-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
     </row>
@@ -520,16 +516,8 @@
           <t>CADIZ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2021-12-28, 2021-12-29, 2022-01-06, 2022-01-11, 2022-01-18, 2022-01-25, 2022-02-01, 2022-02-08, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-15, 2022-03-22, 2022-03-30, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-28, 2022-05-07, 2022-05-18, 2022-05-19, 2022-05-24, 2022-06-02, 2022-06-08, 2022-06-17, 2022-06-22, 2022-06-28, 2022-07-05, 2022-07-12, 2022-07-19, 2022-07-26, 2022-08-02, 2022-08-09, 2022-08-16, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-29, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-27, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-04, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2021-12-28, 2021-12-30, 2022-01-07, 2022-01-18, 2022-01-19, 2022-02-02, 2022-02-03, 2022-02-11, 2022-02-16, 2022-02-23, 2022-02-28, 2022-03-09, 2022-03-10, 2022-03-22, 2022-03-23, 2022-03-29, 2022-04-06, 2022-04-13, 2022-04-20, 2022-04-27, 2022-05-04, 2022-05-11, 2022-05-18, 2022-05-24, 2022-05-25, 2022-06-02, 2022-06-08, 2022-06-21, 2022-06-23, 2022-06-29, 2022-07-05, 2022-07-13, 2022-07-21, 2022-07-27, 2022-08-03, 2022-08-10, 2022-08-17, 2022-08-25, 2022-09-01, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-27, 2022-10-05, 2022-10-12, 2022-10-20, 2022-10-26, 2022-11-02, 2022-11-10, 2022-11-16, 2022-11-24, 2022-12-01, 2022-12-07, 2022-12-14, 2022-12-20, 2022-12-28, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-16, 2023-06-23, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-11, 2023-08-17, 2023-08-24, 2023-08-30, 2023-09-07, 2023-09-14, 2023-09-20, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-20, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-18, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-04, 2024-01-17, 2024-01-22, 2024-01-25, 2024-02-05, 2024-02-10, 2024-02-17, 2024-02-26, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-26, 2025-11-27, 2025-11-28</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -539,12 +527,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-08-12, 2024-08-13, 2024-10-01, 2024-10-15, 2024-10-21, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-08, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-14, 2025-06-25, 2025-07-02, 2025-07-07, 2025-07-14, 2025-07-18, 2025-07-31, 2025-08-04, 2025-08-11, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-08, 2025-10-20, 2025-10-27, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24, 2025-12-01, 2025-12-10, 2025-12-15, 2025-12-22, 2026-01-14, 2026-01-19, 2026-01-27, 2026-02-02, 2026-02-09, 2026-02-16, 2026-02-25, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-08-20, 2024-10-15, 2024-10-17, 2024-11-01, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-13, 2025-01-20, 2025-01-27, 2025-02-07, 2025-02-17, 2025-03-05, 2025-03-07, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-03, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-30, 2025-05-05, 2025-05-14, 2025-05-21, 2025-05-26, 2025-06-05, 2025-06-11, 2025-06-20, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-18, 2025-07-21, 2025-07-31, 2025-08-08, 2025-08-12, 2025-08-25, 2025-09-02, 2025-09-08, 2025-09-18, 2025-09-23, 2025-09-29, 2025-10-06, 2025-10-16, 2025-10-21, 2025-10-30, 2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28, 2025-12-03, 2025-12-11, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-13, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -556,12 +544,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-10-18, 2024-10-21, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2024-12-18, 2025-01-10, 2025-01-16, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-12, 2025-06-20, 2025-07-03, 2025-07-10, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-19, 2025-09-26, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25, 2025-12-12, 2025-12-22, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10-21, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-30, 2024-12-07, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-20, 2025-02-07, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-26, 2025-04-01, 2025-04-09, 2025-04-25, 2025-05-06, 2025-05-19, 2025-05-20, 2025-06-05, 2025-06-06, 2025-06-20, 2025-07-03, 2025-07-04, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-25, 2025-09-02, 2025-09-06, 2025-09-15, 2025-09-19, 2025-09-26, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-19, 2025-11-26, 2025-12-13, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-04</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -573,12 +561,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-09-13, 2023-09-29, 2023-12-28, 2024-01-06, 2024-01-09, 2024-01-19, 2024-01-27, 2024-02-02, 2024-02-10, 2024-02-14, 2024-02-24, 2024-03-02, 2024-03-11, 2024-03-18, 2024-03-23, 2024-04-06, 2024-04-12, 2024-04-17, 2024-04-29, 2024-05-03, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-20, 2024-08-23, 2024-09-03, 2024-09-06, 2024-09-18, 2024-09-20, 2024-10-01, 2024-10-09, 2024-10-11, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-09, 2024-12-14, 2024-12-23, 2024-12-27, 2025-01-08, 2025-01-13, 2025-01-20, 2025-01-24, 2025-01-31, 2025-02-08, 2025-02-14, 2025-02-20, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-22, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-16, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-14, 2025-06-21, 2025-07-01, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-16, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-16, 2025-10-24, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-24, 2025-11-29, 2025-12-03, 2025-12-05, 2025-12-18, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-30, 2026-02-02, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-09, 2026-02-13, 2026-02-20, 2026-02-26, 2026-03-02, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-09, 2026-02-13, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2023-09-29, 2023-12-28, 2024-01-06, 2024-01-12, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-19, 2024-04-06, 2024-04-09, 2024-04-17, 2024-04-22, 2024-04-29, 2024-05-10, 2024-05-14, 2024-05-21, 2024-05-27, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-25, 2024-07-03, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-30, 2024-08-08, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-19, 2024-11-27, 2024-12-06, 2024-12-11, 2024-12-19, 2024-12-27, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-24, 2025-01-31, 2025-02-03, 2025-02-11, 2025-02-18, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-26, 2025-04-03, 2025-04-07, 2025-04-15, 2025-04-23, 2025-05-03, 2025-05-07, 2025-05-13, 2025-05-23, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-17, 2025-06-25, 2025-07-02, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-29, 2025-09-01, 2025-09-12, 2025-09-15, 2025-09-22, 2025-09-30, 2025-10-06, 2025-10-16, 2025-10-24, 2025-10-27, 2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-16, 2025-12-20, 2025-12-22, 2025-12-26, 2026-01-06, 2026-01-17, 2026-01-19, 2026-01-24, 2026-01-31, 2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-23, 2026-02-28, 2026-03-02, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-23, 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -588,16 +576,8 @@
           <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-11, 2024-03-19, 2024-04-02, 2024-04-11, 2024-04-12, 2024-04-23, 2024-05-03, 2024-05-07, 2024-05-14, 2024-05-22, 2024-05-28, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-25, 2024-07-29, 2024-07-31, 2024-08-06, 2024-08-15, 2024-08-16, 2024-08-17, 2024-08-25, 2024-08-27, 2024-09-01, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-26, 2024-10-04, 2024-10-24, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-15, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-26, 2024-12-27, 2025-01-13, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-27, 2025-01-30, 2025-02-10, 2025-02-20, 2025-03-10, 2025-03-17, 2025-03-19, 2025-03-31, 2025-04-01, 2025-04-02, 2025-04-10, 2025-04-21, 2025-04-23, 2025-04-24, 2025-04-28, 2025-05-10, 2025-05-19, 2025-05-21, 2025-05-22, 2025-06-18, 2025-06-19, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-14, 2025-07-17, 2025-07-28, 2025-07-31, 2025-08-04, 2025-08-05, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-02, 2025-09-05, 2025-09-08, 2025-09-20, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2025-11-27, 2026-03-09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2023-08-15, 2023-08-22, 2023-08-29, 2023-09-12, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-15, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-07, 2024-06-13, 2024-06-20, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-07-26, 2024-07-29, 2024-08-01, 2024-08-09, 2024-08-16, 2024-08-17, 2024-08-22, 2024-08-25, 2024-08-30, 2024-09-01, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-28, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-28, 2024-12-05, 2024-12-26, 2024-12-27, 2025-01-16, 2025-01-17, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-19, 2025-02-24, 2025-03-11, 2025-03-18, 2025-03-19, 2025-04-01, 2025-04-02, 2025-04-07, 2025-04-10, 2025-04-23, 2025-04-24, 2025-04-30, 2025-05-10, 2025-05-21, 2025-05-22, 2025-06-19, 2025-06-20, 2025-07-04, 2025-07-07, 2025-07-10, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-29, 2025-08-04, 2025-08-05, 2025-08-06, 2025-08-08, 2025-08-14, 2025-08-19, 2025-08-29, 2025-09-04, 2025-09-05, 2025-09-08, 2025-09-22, 2025-10-10, 2025-10-24, 2025-11-10, 2025-11-14, 2026-03-06, 2026-03-09</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -607,12 +587,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2025-07-02, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-13, 2026-02-25, 2026-02-27</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-13, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2023-08-25, 2025-07-08, 2025-07-15, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-04, 2025-12-12, 2026-01-17, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -624,12 +604,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2022-12-28, 2023-01-06, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-16, 2023-06-22, 2023-06-28, 2023-07-06, 2023-07-13, 2023-07-22, 2023-07-26, 2023-07-31, 2023-08-10, 2023-08-16, 2023-08-25, 2023-09-02, 2023-09-07, 2023-09-13, 2023-09-22, 2023-10-02, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-25, 2023-11-01, 2023-11-09, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-11, 2024-01-16, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-14, 2024-02-21, 2024-03-01, 2024-03-08, 2024-03-13, 2024-03-15, 2024-03-22, 2024-04-04, 2024-04-05, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-07, 2024-05-15, 2024-05-23, 2024-05-30, 2024-06-05, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-08, 2024-10-18, 2024-10-22, 2024-10-28, 2024-11-05, 2024-11-14, 2024-11-21, 2024-11-29, 2025-01-03, 2025-01-16, 2025-03-11, 2025-03-20, 2025-03-25, 2025-03-28, 2025-04-10, 2025-04-22, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-22, 2025-05-29, 2025-06-03, 2025-06-12, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-10, 2025-09-16, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-03</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2023-01-06, 2023-01-13, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-19, 2023-05-26, 2023-05-31, 2023-06-07, 2023-06-16, 2023-06-26, 2023-06-28, 2023-07-07, 2023-07-13, 2023-07-22, 2023-07-26, 2023-08-09, 2023-08-16, 2023-08-18, 2023-08-28, 2023-09-02, 2023-09-07, 2023-09-16, 2023-09-22, 2023-10-02, 2023-10-06, 2023-10-13, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-11, 2023-11-16, 2023-11-24, 2023-11-30, 2023-12-11, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-01, 2024-03-08, 2024-03-14, 2024-03-22, 2024-04-05, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-23, 2024-05-31, 2024-06-06, 2024-06-12, 2024-06-20, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-09, 2024-10-18, 2024-10-25, 2024-10-30, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2025-01-03, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-01, 2025-05-08, 2025-05-13, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-22, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-19, 2025-08-26, 2025-09-04, 2025-09-12, 2025-09-19, 2025-09-23, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-29, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -641,12 +621,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-15, 2024-04-22, 2024-04-27, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-05, 2024-10-10, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-16, 2024-11-23, 2024-11-29, 2024-12-06, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-03, 2025-03-10, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-02, 2025-05-10, 2025-05-19, 2025-05-26, 2025-05-30, 2025-06-09, 2025-06-14, 2025-06-19, 2025-06-27, 2025-06-28, 2025-07-04, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-01, 2025-08-09, 2025-08-15, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-25, 2025-10-29, 2025-11-07, 2025-11-10, 2025-11-21, 2025-11-22, 2025-11-26, 2025-12-06, 2025-12-13, 2025-12-20, 2025-12-22, 2026-01-08, 2026-01-13, 2026-01-22, 2026-02-26, 2026-03-03, 2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-03-20, 2024-03-23, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-13, 2024-05-18, 2024-05-26, 2024-05-31, 2024-06-07, 2024-06-16, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-26, 2024-10-05, 2024-10-11, 2024-10-18, 2024-10-26, 2024-11-01, 2024-11-08, 2024-11-17, 2024-11-23, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-17, 2025-01-24, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-06, 2025-04-13, 2025-04-22, 2025-04-23, 2025-05-04, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-02, 2025-06-09, 2025-06-16, 2025-06-19, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-14, 2025-12-20, 2025-12-22, 2026-01-13, 2026-02-10, 2026-02-28, 2026-03-03, 2026-03-06</t>
+          <t>2026-02-10, 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -656,16 +636,8 @@
           <t>LA CRUZ</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-20, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-25, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-23, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-25, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-07, 2025-07-10, 2025-07-25, 2025-08-13, 2025-09-04, 2025-10-17, 2025-10-24, 2025-11-13, 2025-11-21</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2024-03-04, 2024-03-09, 2024-03-15, 2024-03-23, 2024-04-01, 2024-04-06, 2024-04-13, 2024-04-22, 2024-04-29, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-27, 2024-05-31, 2024-06-07, 2024-06-13, 2024-06-26, 2024-06-28, 2024-07-04, 2024-07-18, 2024-07-19, 2024-07-25, 2024-08-05, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-21, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-23, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-22, 2025-02-27, 2025-03-14, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-25, 2025-05-02, 2025-05-13, 2025-05-19, 2025-05-23, 2025-06-06, 2025-06-14, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-07, 2025-07-25, 2025-08-13, 2025-10-17, 2025-10-18, 2025-10-24, 2025-11-21</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -675,12 +647,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-11-14, 2023-11-16, 2023-11-21, 2023-11-28, 2023-12-07, 2023-12-15, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-08, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-12, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-25, 2024-08-01, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-30, 2024-09-09, 2024-09-13, 2024-09-24, 2024-09-26, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-14, 2024-12-27, 2025-01-24, 2025-02-02, 2025-02-08, 2025-02-13, 2025-02-22, 2025-03-01, 2025-03-03, 2025-03-14, 2025-03-17, 2025-03-30, 2025-04-06, 2025-04-13, 2025-04-23, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-01, 2025-06-05, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-21, 2025-07-27, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-29, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-26, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2023-11-14, 2023-11-17, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-14, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-10, 2024-02-15, 2024-02-23, 2024-03-01, 2024-03-09, 2024-03-15, 2024-03-21, 2024-04-01, 2024-04-06, 2024-04-20, 2024-04-27, 2024-05-05, 2024-05-11, 2024-05-18, 2024-05-26, 2024-06-01, 2024-06-08, 2024-06-15, 2024-06-21, 2024-07-02, 2024-07-13, 2024-07-21, 2024-07-26, 2024-08-03, 2024-08-09, 2024-08-17, 2024-08-26, 2024-08-31, 2024-09-09, 2024-09-14, 2024-09-24, 2024-09-27, 2024-10-05, 2024-10-11, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-09, 2024-11-16, 2024-11-23, 2024-12-01, 2024-12-07, 2024-12-14, 2025-01-18, 2025-01-25, 2025-02-03, 2025-02-08, 2025-02-15, 2025-02-23, 2025-03-01, 2025-03-09, 2025-03-14, 2025-03-22, 2025-03-30, 2025-04-08, 2025-04-13, 2025-04-26, 2025-05-04, 2025-05-11, 2025-05-18, 2025-05-25, 2025-06-02, 2025-06-08, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-13, 2025-07-21, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-24, 2025-08-30, 2025-09-13, 2025-09-17, 2025-09-18, 2025-09-19, 2025-09-24, 2025-09-29, 2025-10-07, 2025-10-16, 2025-10-17, 2025-10-27, 2025-10-28, 2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29, 2026-02-05, 2026-02-28, 2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -692,12 +664,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-05-29, 2024-06-04, 2024-06-11, 2024-06-26, 2024-07-06, 2024-07-12, 2024-07-17, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-08, 2025-01-14, 2025-01-21, 2025-01-29, 2025-02-04, 2025-02-11, 2025-02-20, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-03, 2025-07-09, 2025-07-16, 2025-07-23, 2025-08-01, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-12, 2025-09-17, 2025-09-24, 2025-10-02, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-19, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-06-04, 2024-06-11, 2024-06-22, 2024-06-27, 2024-07-06, 2024-07-12, 2024-07-18, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-07, 2025-03-17, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-04-30, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-12, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -709,12 +681,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-07-02, 2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-10, 2025-12-17, 2026-01-07, 2026-01-14, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-07-18, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-14, 2025-08-20, 2025-09-03, 2025-09-16, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-17, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-12, 2025-11-20, 2025-12-01, 2025-12-04, 2025-12-12, 2026-01-07, 2026-01-10, 2026-01-16, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
     </row>
@@ -726,12 +698,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2022-11-29, 2022-12-16, 2022-12-20, 2022-12-28, 2023-01-13, 2023-01-18, 2023-01-24, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-04, 2023-04-11, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-04, 2023-07-11, 2023-07-19, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-16, 2023-08-22, 2023-08-29, 2023-09-05, 2024-10-16, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-05, 2025-02-10, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-07, 2026-01-22, 2026-01-27, 2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-03</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2022-12-12, 2022-12-19, 2022-12-26, 2022-12-29, 2023-01-13, 2023-01-19, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-11, 2023-04-13, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-15, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-10, 2023-08-16, 2023-08-23, 2023-08-31, 2023-09-05, 2024-11-05, 2025-01-16, 2025-01-23, 2025-01-24, 2025-02-10, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-09, 2025-05-22, 2025-05-29, 2025-06-07, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2026-01-13, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -741,16 +713,8 @@
           <t>LINZ E1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2023-10-23, 2023-11-10, 2023-12-07, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-05, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-19, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-07, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-17, 2025-03-19, 2025-03-25, 2025-04-02, 2025-04-03, 2025-04-23, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-21, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2023-11-10, 2023-12-15, 2024-02-05, 2024-02-12, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-23, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-04, 2024-07-12, 2024-07-19, 2024-07-25, 2024-08-02, 2024-08-09, 2024-08-15, 2024-08-23, 2024-08-29, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-01, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-07, 2024-11-15, 2024-11-21, 2024-11-28, 2024-12-03, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-21, 2025-01-30, 2025-02-05, 2025-02-11, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-17, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -760,14 +724,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-26, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-21, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-20, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-08, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-19, 2023-08-29, 2023-08-30, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-22, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-09, 2024-09-16, 2024-09-24, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-06, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-05, 2024-12-09, 2024-12-16, 2024-12-27, 2025-01-13, 2025-01-20, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-05, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-04, 2025-03-06, 2025-03-10, 2025-03-17, 2025-03-25, 2025-04-01, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-06, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-05, 2025-06-10, 2025-06-17, 2025-06-26, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-02, 2025-11-19, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2022-08-26, 2022-08-31, 2022-09-07, 2022-09-14, 2022-09-21, 2022-09-28, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-29, 2022-12-05, 2022-12-13, 2023-01-03, 2023-01-10, 2023-01-27, 2023-01-30, 2023-01-31, 2023-02-07, 2023-02-14, 2023-02-27, 2023-02-28, 2023-03-13, 2023-03-14, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-11, 2023-04-21, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-24, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-26, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-08, 2024-02-16, 2024-02-22, 2024-03-01, 2024-03-06, 2024-03-13, 2024-03-21, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-07, 2024-06-12, 2024-06-20, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-30, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-08, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-05, 2024-12-11, 2024-12-19, 2025-01-10, 2025-01-17, 2025-01-21, 2025-01-27, 2025-01-28, 2025-01-29, 2025-02-07, 2025-02-12, 2025-02-19, 2025-02-27, 2025-03-04, 2025-03-06, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-21, 2025-05-28, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-26, 2025-07-02, 2025-07-10, 2025-07-17, 2025-07-23, 2025-07-30, 2025-07-31, 2025-08-04, 2025-08-08, 2025-08-09, 2025-08-13, 2025-08-22, 2025-08-25, 2025-08-27, 2025-09-09, 2025-09-12, 2025-09-17, 2025-09-25, 2025-10-09, 2025-11-20, 2026-03-06</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -777,12 +737,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-07, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-28, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-14, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-23, 2025-04-30, 2025-05-02, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-11, 2025-08-26, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-17, 2025-11-19, 2025-11-26, 2025-12-05, 2025-12-10, 2025-12-22, 2025-12-27, 2025-12-29, 2026-01-07, 2026-01-15, 2026-01-21, 2026-01-28, 2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-14, 2026-02-16, 2026-02-18, 2026-02-20, 2026-02-24, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-14, 2026-02-16, 2026-02-18, 2026-02-20, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-09-02, 2023-09-07, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-13, 2023-10-19, 2023-10-27, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-12-01, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-02, 2024-01-05, 2024-01-12, 2024-01-19, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-30, 2024-05-02, 2024-05-11, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-20, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-07, 2025-01-10, 2025-01-13, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-23, 2025-04-24, 2025-05-02, 2025-05-07, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-26, 2025-08-28, 2025-09-10, 2025-09-11, 2025-09-23, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-20, 2025-10-24, 2025-10-30, 2025-11-04, 2025-11-17, 2025-11-20, 2025-12-05, 2025-12-13, 2025-12-22, 2025-12-27, 2026-01-07, 2026-01-13, 2026-01-21, 2026-01-27, 2026-01-30, 2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25, 2026-03-09</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
     </row>
@@ -792,16 +752,8 @@
           <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-08-31, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-28, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-22, 2022-11-28, 2022-12-06, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-18, 2023-01-24, 2023-01-30, 2023-02-08, 2023-02-16, 2023-02-22, 2023-03-03, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-28, 2023-09-06, 2023-09-11, 2023-09-18, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-22, 2023-10-30, 2023-11-06, 2023-11-14, 2023-11-23, 2023-11-27, 2023-12-05, 2023-12-11, 2023-12-27, 2024-01-09, 2024-01-15, 2024-01-24, 2024-01-29, 2024-02-05, 2024-02-14, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-13, 2024-04-17, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-04, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-29, 2024-08-05, 2024-08-09, 2024-08-10, 2024-08-12, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-24, 2024-08-29, 2024-09-02, 2024-09-06, 2024-09-07, 2024-09-14, 2024-09-20, 2024-09-23, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2022-08-09, 2022-08-18, 2022-08-23, 2022-09-02, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-19, 2023-01-31, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-07, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-07-21, 2023-08-02, 2023-08-09, 2023-08-18, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-16, 2023-09-20, 2023-09-29, 2023-10-06, 2023-10-17, 2023-10-18, 2023-10-30, 2023-11-01, 2023-11-08, 2023-11-17, 2023-11-27, 2023-11-30, 2023-12-08, 2023-12-14, 2023-12-28, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-15, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-04, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-15, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-18, 2024-07-19, 2024-07-22, 2024-07-25, 2024-07-27, 2024-08-01, 2024-08-05, 2024-08-08, 2024-08-09, 2024-08-10, 2024-08-13, 2024-08-14, 2024-08-17, 2024-08-22, 2024-08-28, 2024-08-29, 2024-09-03, 2024-09-06, 2024-09-12, 2024-09-20, 2024-10-02, 2024-10-16, 2024-10-24, 2024-10-29, 2024-11-01, 2025-03-05</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -809,16 +761,8 @@
           <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2022-08-03, 2022-08-09, 2022-08-18, 2022-08-23, 2022-08-30, 2022-09-06, 2022-09-15, 2022-09-20, 2022-09-27, 2022-10-04, 2022-10-11, 2022-10-18, 2022-10-24, 2022-10-31, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-13, 2022-12-19, 2022-12-27, 2023-01-04, 2023-01-10, 2023-01-16, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-15, 2023-02-22, 2023-02-28, 2023-03-08, 2023-03-13, 2023-03-21, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-30, 2023-06-05, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-10, 2023-07-19, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-24, 2023-12-04, 2023-12-11, 2023-12-18, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-07, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-04, 2024-04-08, 2024-04-15, 2024-04-23, 2024-04-29, 2024-05-03, 2024-05-05, 2024-05-17, 2024-05-21, 2024-05-27, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-15, 2024-07-22, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-12, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-13, 2024-09-25, 2024-10-29, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2022-08-05, 2022-08-09, 2022-08-18, 2022-08-23, 2022-09-01, 2022-09-07, 2022-09-19, 2022-09-20, 2022-09-30, 2022-10-05, 2022-10-12, 2022-10-19, 2022-10-26, 2022-11-02, 2022-11-08, 2022-11-15, 2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-06, 2023-01-12, 2023-01-18, 2023-01-26, 2023-02-02, 2023-02-13, 2023-02-16, 2023-02-24, 2023-03-03, 2023-03-09, 2023-03-15, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-12, 2023-04-27, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-08, 2023-07-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-08, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-16, 2023-10-20, 2023-10-26, 2023-11-02, 2023-11-13, 2023-11-15, 2023-11-29, 2023-12-07, 2023-12-18, 2023-12-20, 2023-12-28, 2024-01-03, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-09, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-13, 2024-04-18, 2024-04-26, 2024-05-02, 2024-05-05, 2024-05-09, 2024-05-17, 2024-05-21, 2024-05-28, 2024-05-30, 2024-06-12, 2024-06-13, 2024-06-17, 2024-06-28, 2024-07-04, 2024-07-13, 2024-07-17, 2024-07-23, 2024-07-29, 2024-07-30, 2024-08-05, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-04, 2024-09-25, 2024-11-01, 2025-02-24, 2025-03-05</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -828,12 +772,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-05-28, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-06-04, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-12, 2025-08-20, 2025-09-02, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-10, 2025-10-17, 2025-10-23, 2025-10-29, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27, 2025-12-05, 2025-12-11, 2025-12-18, 2025-12-26, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -845,12 +789,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2022-09-02, 2022-09-06, 2022-09-13, 2022-09-20, 2022-09-27, 2022-10-11, 2022-10-18, 2022-10-25, 2022-11-01, 2022-11-08, 2022-11-15, 2022-11-21, 2022-11-28, 2022-12-05, 2022-12-12, 2022-12-19, 2022-12-26, 2023-01-02, 2023-01-10, 2023-01-16, 2023-01-23, 2023-01-30, 2023-02-06, 2023-02-13, 2023-02-22, 2023-02-23, 2023-03-07, 2023-03-15, 2023-03-23, 2023-03-29, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-05, 2024-03-13, 2024-03-19, 2024-04-02, 2024-04-10, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-16, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-13, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-15, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-02, 2025-07-08, 2025-07-17, 2025-07-22, 2025-07-29, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-02, 2025-09-09, 2025-09-24, 2025-09-30, 2025-10-06, 2025-10-07, 2025-10-14, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28, 2025-12-01, 2025-12-03, 2025-12-05, 2025-12-09, 2025-12-15, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2022-09-08, 2022-09-15, 2022-09-21, 2022-09-28, 2022-10-12, 2022-10-19, 2022-10-29, 2022-11-02, 2022-11-09, 2022-11-16, 2022-11-25, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-26, 2022-12-27, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-26, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-31, 2023-06-01, 2023-06-09, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-26, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-21, 2023-12-27, 2024-01-03, 2024-01-12, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-04, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-06, 2024-06-12, 2024-06-18, 2024-06-27, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-12, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-09, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-30, 2025-09-04, 2025-09-16, 2025-09-25, 2025-10-02, 2025-10-06, 2025-10-10, 2025-10-17, 2025-10-21, 2025-10-22, 2025-10-24, 2025-10-30, 2025-11-07, 2025-11-11, 2025-11-13, 2025-11-18, 2025-11-21, 2025-11-26, 2025-11-28, 2025-12-03, 2025-12-05, 2025-12-11, 2025-12-19, 2025-12-22, 2026-01-02, 2026-01-07, 2026-01-13, 2026-01-17, 2026-01-23, 2026-01-24, 2026-01-30, 2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26, 2026-03-04, 2026-03-06</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -862,12 +806,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2022-11-22, 2022-11-30, 2022-12-06, 2022-12-13, 2022-12-20, 2022-12-28, 2023-01-03, 2023-01-10, 2023-01-17, 2023-01-24, 2023-01-31, 2023-02-08, 2023-02-14, 2023-02-21, 2023-02-28, 2023-03-07, 2023-03-14, 2023-03-21, 2023-03-28, 2023-04-04, 2023-04-11, 2023-04-18, 2023-04-25, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-04, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-15, 2023-08-22, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-03, 2023-10-05, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-09, 2024-01-12, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-13, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-27, 2024-12-03, 2024-12-10, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2022-11-26, 2022-11-30, 2022-12-09, 2022-12-14, 2022-12-21, 2022-12-28, 2023-01-04, 2023-01-12, 2023-01-18, 2023-01-25, 2023-02-03, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-12, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-22, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-20, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-29, 2024-09-04, 2024-09-13, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-24, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-27, 2024-12-04, 2024-12-11, 2025-01-09, 2025-09-26, 2025-10-08, 2025-10-14, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2026-01-13, 2026-01-30, 2026-02-03, 2026-02-24, 2026-02-27, 2026-03-03, 2026-03-10</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -879,12 +823,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-15, 2023-08-25, 2023-08-27, 2023-08-30, 2023-09-06, 2023-10-05, 2023-10-19, 2023-10-26, 2023-11-03, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-04, 2024-01-12, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-09, 2024-02-15, 2024-02-22, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2024-12-23, 2024-12-30, 2025-01-07, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-30, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-13, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-06, 2025-08-14, 2025-08-20, 2025-08-27, 2025-09-02, 2025-09-09, 2025-09-17, 2025-09-24, 2025-09-29, 2025-10-02, 2025-10-07, 2025-10-14, 2025-10-15, 2025-10-17, 2025-10-21, 2025-10-24, 2025-10-27, 2025-10-28, 2025-11-05, 2025-11-07, 2025-11-11, 2025-11-12, 2025-11-19, 2025-11-25, 2025-11-28, 2025-12-03, 2025-12-10, 2025-12-27, 2026-01-06, 2026-01-26, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2023-08-28, 2023-08-30, 2023-09-06, 2023-10-13, 2023-10-20, 2023-10-31, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-25, 2023-11-30, 2023-12-07, 2023-12-15, 2023-12-21, 2024-01-04, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-03, 2024-02-15, 2024-02-19, 2024-02-24, 2024-03-02, 2024-03-08, 2024-03-15, 2024-03-27, 2024-04-03, 2024-04-10, 2024-04-22, 2024-04-24, 2024-05-02, 2024-05-14, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-12, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-18, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-09, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-02, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-21, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-05, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-27, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-15, 2025-10-17, 2025-10-24, 2025-10-27, 2025-10-31, 2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-27, 2025-11-28, 2025-12-03, 2025-12-04, 2025-12-12, 2025-12-27, 2026-01-09, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
     </row>
@@ -894,16 +838,8 @@
           <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2022-11-23, 2022-11-30, 2022-12-07, 2022-12-14, 2022-12-21, 2022-12-29, 2023-01-04, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-22, 2023-03-29, 2023-04-04, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-10, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-03-27, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-16, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-14, 2025-07-21, 2025-07-28, 2025-08-04, 2025-08-12, 2025-08-19, 2025-08-25, 2025-09-01, 2025-09-08, 2025-09-15, 2025-09-23, 2025-09-29, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-10, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2022-11-24, 2022-12-01, 2022-12-09, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-03, 2023-03-10, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-05, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-10, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2024-01-03, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-12, 2024-08-20, 2024-08-26, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-09, 2024-12-17, 2025-01-07, 2025-01-14, 2025-01-20, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-03, 2025-03-10, 2025-03-17, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-14, 2025-04-21, 2025-04-28, 2025-05-05, 2025-05-12, 2025-05-19, 2025-05-26, 2025-06-03, 2025-06-09, 2025-06-16, 2025-06-24, 2025-07-01, 2025-07-07, 2025-07-15, 2025-07-21, 2025-07-28, 2025-08-06, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-03, 2025-09-08, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-08, 2025-10-21, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24, 2025-12-09, 2025-12-18, 2025-12-23, 2025-12-29, 2026-01-07, 2026-01-14</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -913,12 +849,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-03, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-17, 2023-07-25, 2023-08-01, 2023-08-08, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-05, 2023-09-11, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-24, 2023-10-30, 2023-11-08, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-27, 2024-01-03, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-06, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-03, 2024-07-08, 2024-07-10, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-27, 2024-09-02, 2024-09-09, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-07, 2024-10-15, 2024-10-21, 2024-10-28, 2024-11-08, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-13, 2025-05-29, 2025-06-19, 2025-07-07, 2025-07-14, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-12, 2025-08-29, 2025-09-11, 2025-09-16, 2025-09-22, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2022-12-26, 2022-12-29, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-18, 2023-07-25, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-29, 2023-09-05, 2023-09-12, 2023-09-20, 2023-09-26, 2023-10-03, 2023-10-13, 2023-10-17, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-12, 2023-12-19, 2023-12-27, 2024-01-05, 2024-01-10, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-22, 2024-03-01, 2024-03-07, 2024-03-12, 2024-03-19, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-28, 2024-06-05, 2024-06-12, 2024-06-18, 2024-06-25, 2024-07-03, 2024-07-10, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-14, 2024-08-23, 2024-08-29, 2024-09-03, 2024-09-11, 2024-09-17, 2024-09-24, 2024-10-02, 2024-10-09, 2024-10-17, 2024-10-25, 2024-10-30, 2024-11-26, 2024-12-03, 2024-12-10, 2025-01-03, 2025-01-17, 2025-03-14, 2025-05-30, 2025-07-07, 2025-07-14, 2025-07-28, 2025-07-31, 2025-08-06, 2025-08-15, 2025-09-05, 2025-09-11, 2025-09-16, 2025-09-23, 2025-10-04, 2025-10-09, 2025-10-15, 2025-10-23, 2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24, 2025-12-02, 2025-12-04, 2025-12-10, 2025-12-17, 2026-01-14, 2026-01-19, 2026-01-20, 2026-01-26, 2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24, 2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
     </row>
@@ -928,16 +864,8 @@
           <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2022-11-17, 2022-12-01, 2022-12-15, 2023-02-03, 2023-02-10, 2023-02-16, 2023-02-23, 2023-03-01, 2023-03-07, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-23, 2023-06-29, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-17, 2023-08-25, 2023-08-31, 2023-09-08, 2023-09-15, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2024-12-23</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2022-11-24, 2022-12-01, 2023-02-02, 2023-02-03, 2023-02-13, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-11, 2023-03-17, 2023-03-25, 2023-03-31, 2023-04-14, 2023-04-27, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-08-02, 2023-08-05, 2023-08-11, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-25, 2023-10-27, 2023-11-17, 2023-11-24, 2023-12-06, 2024-02-02</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -947,12 +875,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2023-03-14, 2023-03-21, 2023-03-28, 2023-04-03, 2023-04-10, 2023-04-24, 2023-05-02, 2023-05-09, 2023-05-16, 2023-05-23, 2023-05-30, 2023-06-06, 2023-06-13, 2023-06-20, 2023-06-27, 2023-07-05, 2023-07-11, 2023-07-18, 2023-07-25, 2023-08-01, 2023-08-09, 2023-08-14, 2023-08-22, 2023-08-28, 2023-09-04, 2023-09-11, 2023-09-18, 2023-09-25, 2023-10-02, 2023-10-09, 2023-10-17, 2023-10-23, 2023-10-30, 2023-11-07, 2023-11-14, 2023-11-20, 2023-11-27, 2023-12-04, 2023-12-11, 2023-12-18, 2024-01-09, 2024-01-15, 2024-01-22, 2024-01-29, 2024-02-05, 2024-02-12, 2024-02-19, 2024-02-26, 2024-03-04, 2024-03-11, 2024-03-18, 2024-04-01, 2024-04-08, 2024-04-15, 2024-04-22, 2024-04-29, 2024-05-07, 2024-05-14, 2024-05-20, 2024-05-27, 2024-06-04, 2024-06-11, 2024-06-17, 2024-06-24, 2024-07-02, 2024-07-08, 2024-07-15, 2024-07-22, 2024-07-29, 2024-08-05, 2024-08-12, 2024-08-20, 2024-08-23, 2024-09-02, 2024-09-10, 2024-09-16, 2024-09-23, 2024-09-30, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-25, 2024-11-05, 2024-11-12, 2024-11-18, 2024-11-25, 2024-12-02, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-14, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-04, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-23, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-28, 2025-06-03, 2025-06-10, 2025-06-18, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-23, 2025-07-29, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-10-01, 2025-10-09, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-20, 2025-11-26, 2025-12-03, 2025-12-09, 2025-12-18, 2026-01-14, 2026-01-20, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2023-03-15, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-13, 2023-04-26, 2023-05-04, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-28, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-09, 2024-04-17, 2024-04-24, 2024-04-30, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-06, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-05, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-21, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -964,12 +892,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2022-12-07, 2022-12-15, 2022-12-22, 2022-12-29, 2023-01-05, 2023-01-12, 2023-01-19, 2023-01-26, 2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-11, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-18, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-04, 2023-11-15, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-21, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-05, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-10, 2024-03-17, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-03, 2024-05-08, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-15, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-26, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-31, 2024-11-05, 2024-11-11, 2024-11-16, 2024-11-28, 2024-12-03, 2024-12-10, 2025-01-09, 2025-01-14, 2025-01-21, 2025-01-30, 2025-02-07, 2025-02-14, 2025-02-22, 2025-03-01, 2025-03-18, 2025-04-12, 2025-04-24, 2025-06-19, 2025-12-26, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-13, 2026-01-20, 2026-01-21, 2026-01-22, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-02-17, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-02-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2022-12-09, 2022-12-16, 2022-12-22, 2022-12-30, 2023-01-06, 2023-01-13, 2023-01-20, 2023-01-27, 2023-02-03, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-29, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-10, 2023-06-20, 2023-06-26, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-16, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-16, 2023-12-21, 2023-12-28, 2024-01-05, 2024-01-13, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-17, 2024-02-23, 2024-03-03, 2024-03-08, 2024-03-16, 2024-04-04, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-27, 2024-05-03, 2024-05-11, 2024-05-18, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-23, 2024-06-27, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-01, 2024-08-10, 2024-08-15, 2024-08-24, 2024-08-26, 2024-08-30, 2024-09-05, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-05, 2024-10-09, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-21, 2024-11-30, 2024-12-07, 2024-12-13, 2025-01-10, 2025-01-20, 2025-01-25, 2025-02-01, 2025-02-07, 2025-02-14, 2025-02-24, 2025-03-01, 2025-03-26, 2025-04-24, 2025-06-04, 2025-07-04, 2025-12-26, 2025-12-29, 2025-12-30, 2026-01-02, 2026-01-05, 2026-01-09, 2026-01-19, 2026-01-20, 2026-01-21, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-30, 2026-01-31, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16, 2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
     </row>
@@ -981,12 +909,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2023-08-14, 2023-08-25, 2023-08-27, 2024-02-14, 2024-02-21, 2024-02-29, 2024-03-07, 2024-03-12, 2024-03-21, 2024-03-27, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-17, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-22, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-19, 2024-11-26, 2024-12-05, 2024-12-10, 2024-12-17, 2024-12-27, 2025-01-15, 2025-01-21, 2025-01-28, 2025-02-06, 2025-02-11, 2025-02-18, 2025-02-26, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-06, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-28, 2025-08-05, 2025-08-12, 2025-08-19, 2025-08-26, 2025-09-02, 2025-09-04, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-28, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25, 2025-12-02, 2025-12-09, 2025-12-16, 2025-12-23, 2025-12-30, 2026-01-06, 2026-01-13, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-10, 2026-02-17, 2026-02-19, 2026-02-24, 2026-03-03, 2026-03-05</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2023-08-25, 2024-01-31, 2024-02-16, 2024-02-24, 2024-03-01, 2024-03-09, 2024-03-16, 2024-03-23, 2024-03-27, 2024-04-04, 2024-04-13, 2024-04-20, 2024-04-27, 2024-05-04, 2024-05-10, 2024-05-18, 2024-05-25, 2024-06-01, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-29, 2024-07-06, 2024-07-12, 2024-07-19, 2024-07-27, 2024-08-06, 2024-08-10, 2024-08-16, 2024-08-25, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-25, 2024-10-04, 2024-10-12, 2024-10-18, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-27, 2024-12-07, 2024-12-12, 2024-12-18, 2025-01-09, 2025-01-17, 2025-01-22, 2025-01-29, 2025-02-08, 2025-02-13, 2025-02-21, 2025-02-27, 2025-03-07, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-11, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-06, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-02, 2025-07-11, 2025-07-17, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-15, 2025-08-21, 2025-08-29, 2025-09-03, 2025-09-11, 2025-09-19, 2025-09-24, 2025-10-01, 2025-10-09, 2025-10-15, 2025-10-25, 2025-10-31, 2025-11-06, 2025-11-11, 2025-11-21, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-17, 2025-12-27, 2026-01-03, 2026-01-09, 2026-01-16, 2026-01-26, 2026-01-29, 2026-02-07, 2026-02-12, 2026-02-19, 2026-02-24, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-07, 2026-02-12, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
     </row>
@@ -998,12 +926,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2023-08-14, 2025-12-22, 2025-12-26, 2026-01-02, 2026-01-07, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025-12-26, 2026-01-02, 2026-01-08, 2026-01-16, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1015,12 +943,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-10-31, 2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-26, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12, 2025-12-04, 2025-12-17, 2025-12-27, 2026-01-09, 2026-01-10, 2026-01-13, 2026-01-27, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
     </row>
@@ -1032,12 +960,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2023-06-07, 2023-06-14, 2023-06-21, 2023-06-29, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-09, 2023-08-16, 2023-08-24, 2023-08-30, 2023-09-06, 2023-09-13, 2023-09-20, 2023-09-26, 2023-10-05, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-16, 2023-11-22, 2023-11-29, 2023-12-07, 2023-12-13, 2023-12-27, 2024-01-03, 2024-01-10, 2024-01-17, 2024-01-24, 2024-02-01, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-30, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-11, 2024-09-18, 2024-09-25, 2024-10-02, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-28, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-27, 2024-12-04, 2024-12-12, 2024-12-20, 2025-01-08, 2025-01-15, 2025-01-22, 2025-01-30, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-05, 2025-03-11, 2025-03-20, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-20, 2025-08-28, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-25, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27, 2025-12-04, 2025-12-10, 2025-12-18, 2026-01-14, 2026-01-22, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25, 2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-21, 2023-07-28, 2023-08-03, 2023-08-10, 2023-08-18, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-06, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-17, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2023-12-28, 2024-01-04, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-02, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-20, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-25, 2025-05-03, 2025-05-08, 2025-05-15, 2025-05-24, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-10-02, 2025-10-22, 2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-12, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-30, 2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1047,16 +975,8 @@
           <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-10, 2023-11-17, 2024-08-06, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-23, 2024-12-27, 2025-01-10, 2025-01-17, 2025-02-07, 2025-02-14, 2025-02-28, 2025-03-07, 2025-03-17, 2025-03-21, 2025-04-09, 2025-05-17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-21, 2023-10-28, 2023-11-03, 2023-11-14, 2023-11-17, 2024-08-16, 2024-08-30, 2024-09-06, 2024-09-09, 2024-09-20, 2024-09-25, 2024-10-03, 2024-10-08, 2024-10-17, 2024-10-25, 2024-10-29, 2024-11-06, 2024-11-13, 2024-12-04, 2024-12-09, 2024-12-18, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-02-12, 2025-02-17, 2025-03-05, 2025-03-12, 2025-03-20, 2025-03-27, 2025-04-11</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1066,12 +986,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-06-12, 2024-06-19, 2024-06-24, 2024-07-04, 2024-07-11, 2024-07-17, 2024-07-24, 2024-08-01, 2024-08-08, 2024-08-14, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-12, 2024-09-18, 2024-09-25, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-15, 2024-11-20, 2024-11-28, 2024-12-05, 2024-12-11, 2024-12-19, 2024-12-26, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-03, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-10, 2025-07-16, 2025-07-23, 2025-07-31, 2025-08-06, 2025-08-13, 2025-08-21, 2025-09-03, 2025-09-11, 2025-09-18, 2025-09-24, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-27, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-20, 2025-11-26, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-28, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-04</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-06-12, 2024-06-21, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-17, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-12, 2024-12-19, 2024-12-26, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-06, 2025-10-09, 2025-10-17, 2025-10-29, 2025-10-30, 2025-11-06, 2025-11-14, 2025-11-21, 2025-11-27, 2025-12-05, 2025-12-11, 2026-01-16, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1003,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-12-12, 2024-12-21, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-22, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-08, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-20, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-15, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29, 2025-12-05, 2025-12-11, 2025-12-19, 2026-01-17, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-14, 2026-02-20, 2026-02-24, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-01-07, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-31, 2025-02-07, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-08, 2025-03-14, 2025-03-22, 2025-03-27, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-06, 2025-06-13, 2025-06-21, 2025-06-27, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29, 2025-12-06, 2025-12-12, 2026-01-17, 2026-01-23, 2026-01-31, 2026-02-06, 2026-02-14, 2026-02-21, 2026-02-28, 2026-03-06</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1020,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2023-08-14, 2024-08-20, 2025-01-15, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-26, 2025-03-05, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-09, 2025-04-16, 2025-04-24, 2025-05-07, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-18, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-15, 2025-07-23, 2025-07-25, 2025-08-02, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-21, 2025-10-24, 2025-10-28, 2025-10-29, 2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-20, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-02-22, 2025-01-15, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-19, 2025-03-26, 2025-04-03, 2025-04-09, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-14, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-02, 2025-08-06, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-24, 2025-10-29, 2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27, 2025-12-05, 2025-12-12, 2026-01-09, 2026-01-22, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27, 2026-03-06</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1132,16 +1052,8 @@
           <t>PRUEBA</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1151,12 +1063,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2023-09-07, 2023-09-12, 2023-09-19, 2023-09-25, 2023-10-03, 2023-10-10, 2023-10-17, 2023-10-24, 2023-10-31, 2023-11-07, 2023-11-14, 2023-11-21, 2023-11-28, 2023-12-05, 2023-12-12, 2023-12-19, 2024-01-09, 2024-01-16, 2024-01-23, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-20, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-23, 2024-04-25, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-18, 2024-06-25, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-09-03, 2024-09-10, 2024-09-18, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-22, 2024-10-29, 2024-11-05, 2024-11-12, 2024-11-20, 2024-11-26, 2024-12-03, 2024-12-10, 2024-12-17, 2025-01-16, 2025-01-21, 2025-01-28, 2025-02-04, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-04-30, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-29, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2025-12-27, 2026-01-14, 2026-01-22, 2026-01-29, 2026-02-03, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2023-09-07, 2023-09-12, 2023-09-20, 2023-09-27, 2023-10-04, 2023-10-11, 2023-10-18, 2023-10-25, 2023-11-01, 2023-11-08, 2023-11-15, 2023-11-23, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2024-01-10, 2024-01-17, 2024-01-24, 2024-01-31, 2024-02-07, 2024-02-15, 2024-02-21, 2024-02-29, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-10, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-03, 2024-07-10, 2024-07-21, 2024-07-25, 2024-07-31, 2024-08-08, 2024-08-15, 2024-08-21, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-19, 2024-09-25, 2024-10-02, 2024-10-11, 2024-10-16, 2024-10-23, 2024-10-30, 2024-11-06, 2024-11-13, 2024-11-20, 2024-11-28, 2024-12-04, 2024-12-11, 2025-01-10, 2025-01-16, 2025-01-22, 2025-01-29, 2025-02-05, 2025-02-12, 2025-02-19, 2025-02-28, 2025-03-07, 2025-03-20, 2025-03-21, 2025-03-28, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-30, 2025-06-07, 2025-06-13, 2025-06-26, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-22, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-24, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-19, 2025-12-27, 2026-01-14, 2026-01-24, 2026-02-02, 2026-02-03, 2026-02-09, 2026-02-18, 2026-02-21, 2026-03-03, 2026-03-06, 2026-03-16</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-18, 2026-02-21</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1080,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2023-08-04, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-04, 2025-04-10, 2025-04-25, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-08, 2025-08-13, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-18, 2026-02-26, 2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2023-08-31, 2024-10-25, 2024-11-02, 2024-11-08, 2024-11-14, 2024-11-21, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-19, 2025-01-10, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-03-06, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-27, 2025-04-04, 2025-04-12, 2025-04-26, 2025-05-02, 2025-05-08, 2025-05-15, 2025-05-22, 2025-05-31, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-27, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-24, 2025-08-01, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-15, 2026-01-24, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1097,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2023-08-01, 2023-08-29, 2025-02-11, 2025-02-18, 2025-02-25, 2025-03-05, 2025-03-11, 2025-03-18, 2025-03-25, 2025-04-01, 2025-04-08, 2025-04-22, 2025-04-29, 2025-05-08, 2025-05-13, 2025-05-20, 2025-05-27, 2025-06-03, 2025-06-10, 2025-06-17, 2025-06-24, 2025-07-01, 2025-07-08, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-09, 2025-09-16, 2025-09-23, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-29, 2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25, 2025-12-02, 2026-01-19, 2026-01-20, 2026-01-27, 2026-02-03, 2026-02-11, 2026-02-18, 2026-02-24, 2026-03-03, 2026-03-10, 2026-03-17</t>
+          <t>2026-02-03, 2026-02-11, 2026-02-18, 2026-02-24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2025-02-05, 2025-02-11, 2025-02-19, 2025-02-27, 2025-03-05, 2025-03-12, 2025-03-19, 2025-03-26, 2025-04-02, 2025-04-10, 2025-04-24, 2025-05-07, 2025-05-08, 2025-05-14, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-11, 2025-06-19, 2025-06-25, 2025-07-02, 2025-07-09, 2025-07-16, 2025-07-23, 2025-07-30, 2025-08-06, 2025-08-13, 2025-08-20, 2025-08-27, 2025-09-03, 2025-09-10, 2025-09-17, 2025-09-24, 2025-10-01, 2025-10-08, 2025-10-15, 2025-10-22, 2025-10-29, 2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26, 2026-01-13, 2026-01-19, 2026-01-21, 2026-01-28, 2026-02-04, 2026-02-11, 2026-02-21, 2026-02-25, 2026-03-04, 2026-03-11, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-21, 2026-02-25</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1114,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2023-02-02, 2023-02-09, 2023-02-16, 2023-02-23, 2023-03-02, 2023-03-09, 2023-03-16, 2023-03-23, 2023-03-30, 2023-04-13, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-11, 2023-05-18, 2023-05-25, 2023-06-01, 2023-06-08, 2023-06-15, 2023-06-22, 2023-06-29, 2023-07-06, 2023-07-13, 2023-07-19, 2023-07-27, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-08-31, 2023-09-07, 2023-09-14, 2023-09-21, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-19, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-07, 2023-12-14, 2024-01-11, 2024-01-18, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-13, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-24, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-29, 2024-12-05, 2024-12-12, 2024-12-19, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-14, 2025-02-21, 2025-02-27, 2025-03-06, 2025-03-14, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-15, 2025-05-23, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-11, 2025-07-17, 2025-07-24, 2025-07-31, 2025-08-07, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-04, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-07, 2025-11-13, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-12, 2025-12-20, 2026-01-15, 2026-01-22, 2026-02-21, 2026-02-26, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-21, 2026-02-26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2023-02-02, 2023-02-10, 2023-02-17, 2023-02-24, 2023-03-03, 2023-03-10, 2023-03-17, 2023-03-24, 2023-03-31, 2023-04-14, 2023-04-21, 2023-04-28, 2023-05-05, 2023-05-12, 2023-05-19, 2023-05-26, 2023-06-02, 2023-06-09, 2023-06-16, 2023-06-23, 2023-06-30, 2023-07-07, 2023-07-14, 2023-07-21, 2023-07-28, 2023-08-04, 2023-08-11, 2023-08-18, 2023-08-25, 2023-09-01, 2023-09-08, 2023-09-15, 2023-09-22, 2023-09-29, 2023-10-06, 2023-10-13, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-10, 2023-11-17, 2023-11-24, 2023-12-01, 2023-12-07, 2023-12-15, 2024-01-18, 2024-01-19, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2025-12-20, 2026-01-16, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1131,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2022-11-30, 2022-12-07, 2022-12-13, 2022-12-21, 2022-12-30, 2023-01-11, 2023-01-18, 2023-01-25, 2023-02-01, 2023-02-08, 2023-02-15, 2023-02-22, 2023-03-01, 2023-03-08, 2023-03-15, 2023-03-21, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-19, 2023-04-26, 2023-05-03, 2023-05-10, 2023-05-17, 2023-05-24, 2023-05-31, 2023-06-07, 2023-06-14, 2023-06-21, 2023-06-27, 2023-07-05, 2023-07-12, 2023-07-19, 2023-07-26, 2023-08-02, 2023-08-09, 2023-08-16, 2023-08-23, 2023-08-30, 2023-09-04, 2023-09-13, 2023-09-21, 2023-09-27, 2023-10-04, 2023-10-10, 2023-10-18, 2023-10-25, 2023-10-31, 2023-11-08, 2023-11-15, 2023-11-22, 2023-11-29, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-27, 2024-01-10, 2024-01-25, 2024-01-31, 2024-02-07, 2024-02-14, 2024-02-20, 2024-02-28, 2024-03-06, 2024-03-12, 2024-03-19, 2024-04-03, 2024-04-09, 2024-04-16, 2024-04-23, 2024-05-02, 2024-05-07, 2024-05-14, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-26, 2024-07-02, 2024-07-09, 2024-07-16, 2024-07-24, 2024-07-30, 2024-08-06, 2024-08-13, 2024-08-20, 2024-08-27, 2024-08-30, 2024-09-03, 2024-09-10, 2024-09-17, 2024-09-24, 2024-10-01, 2024-10-08, 2024-10-15, 2024-10-21, 2024-10-29, 2024-11-05, 2024-11-13, 2024-11-19, 2024-11-26, 2024-12-02, 2024-12-10, 2024-12-17, 2025-01-07, 2025-01-15, 2025-01-22, 2025-01-27, 2025-02-03, 2025-02-10, 2025-02-17, 2025-02-24, 2025-03-05, 2025-03-10, 2025-03-18, 2025-03-25, 2025-03-31, 2025-04-07, 2025-04-21, 2025-04-28, 2025-05-07, 2025-05-13, 2025-05-21, 2025-05-28, 2025-06-04, 2025-06-13, 2025-06-18, 2025-06-25, 2025-07-01, 2025-07-09, 2025-07-15, 2025-07-22, 2025-07-30, 2025-08-05, 2025-08-12, 2025-08-20, 2025-08-26, 2025-09-02, 2025-09-08, 2025-09-16, 2025-09-25, 2025-09-30, 2025-10-07, 2025-10-14, 2025-10-22, 2025-10-28, 2025-11-04, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-17, 2026-01-22, 2026-01-27, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2022-12-02, 2022-12-07, 2022-12-14, 2022-12-22, 2022-12-30, 2023-01-11, 2023-01-20, 2023-01-25, 2023-02-02, 2023-02-08, 2023-02-17, 2023-02-22, 2023-03-01, 2023-03-09, 2023-03-16, 2023-03-22, 2023-03-29, 2023-04-05, 2023-04-12, 2023-04-20, 2023-04-27, 2023-05-04, 2023-05-12, 2023-05-17, 2023-05-25, 2023-05-31, 2023-06-08, 2023-06-14, 2023-06-22, 2023-06-29, 2023-07-05, 2023-07-13, 2023-07-19, 2023-07-26, 2023-08-03, 2023-08-10, 2023-08-17, 2023-08-24, 2023-09-01, 2023-09-07, 2023-09-14, 2023-09-22, 2023-09-28, 2023-10-05, 2023-10-12, 2023-10-18, 2023-10-26, 2023-11-02, 2023-11-09, 2023-11-16, 2023-11-23, 2023-11-30, 2023-12-06, 2023-12-13, 2023-12-20, 2023-12-28, 2024-01-12, 2024-01-25, 2024-02-01, 2024-02-08, 2024-02-14, 2024-02-21, 2024-02-28, 2024-03-06, 2024-03-13, 2024-03-20, 2024-04-03, 2024-04-11, 2024-04-17, 2024-04-24, 2024-05-02, 2024-05-08, 2024-05-15, 2024-05-22, 2024-05-29, 2024-06-05, 2024-06-12, 2024-06-19, 2024-06-26, 2024-07-04, 2024-07-10, 2024-07-17, 2024-07-24, 2024-07-31, 2024-08-08, 2024-08-13, 2024-08-21, 2024-08-28, 2024-09-03, 2024-09-05, 2024-09-11, 2024-09-18, 2024-09-24, 2024-10-08, 2024-10-09, 2024-10-16, 2024-10-23, 2024-10-31, 2024-11-06, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-04, 2024-12-12, 2024-12-18, 2025-01-08, 2025-01-16, 2025-01-22, 2025-01-28, 2025-02-06, 2025-02-13, 2025-02-19, 2025-02-26, 2025-03-10, 2025-03-12, 2025-03-19, 2025-03-27, 2025-04-02, 2025-04-09, 2025-04-23, 2025-04-30, 2025-05-07, 2025-05-14, 2025-05-22, 2025-05-28, 2025-06-05, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-01, 2025-07-10, 2025-07-16, 2025-07-25, 2025-08-02, 2025-08-11, 2025-08-13, 2025-08-21, 2025-08-27, 2025-09-04, 2025-09-10, 2025-09-17, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-20, 2025-10-24, 2025-10-28, 2025-11-05, 2025-11-12, 2025-11-19, 2025-12-03, 2025-12-19, 2026-01-22, 2026-01-28, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-11</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1148,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-01-12, 2024-01-26, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-02-29, 2024-03-05, 2024-03-14, 2024-03-21, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-07, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-10-31, 2024-11-07, 2024-11-14, 2024-11-21, 2024-11-28, 2024-12-05, 2024-12-13, 2025-01-09, 2025-01-16, 2025-01-23, 2025-01-30, 2025-02-06, 2025-02-13, 2025-02-20, 2025-02-27, 2025-03-06, 2025-03-13, 2025-03-20, 2025-03-27, 2025-04-03, 2025-04-10, 2025-04-24, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-22, 2025-05-29, 2025-06-05, 2025-06-12, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-18, 2025-07-24, 2025-07-28, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-27, 2025-09-05, 2025-09-11, 2025-09-26, 2025-10-09, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-16, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-19, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-01-26, 2024-01-30, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-23, 2024-03-01, 2024-03-08, 2024-03-15, 2024-03-22, 2024-04-05, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-21, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-20, 2024-09-27, 2024-10-04, 2024-10-11, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-26, 2025-10-11, 2025-10-18, 2025-10-24, 2025-10-31, 2025-11-06, 2025-11-21, 2025-11-28, 2025-12-06, 2025-12-19, 2026-01-09, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-14</t>
+          <t>2026-02-06, 2026-02-09, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1165,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-10-01, 2025-10-15, 2025-10-29, 2025-11-12, 2025-11-19, 2025-12-03, 2026-01-07, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-02, 2026-03-09, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025-10-01, 2025-10-29, 2025-11-12, 2025-11-14, 2025-12-03, 2026-01-21, 2026-02-04, 2026-02-11, 2026-02-23, 2026-03-09, 2026-03-18</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-23</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1182,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2023-02-10, 2023-02-16, 2023-02-24, 2023-03-06, 2023-03-13, 2023-03-21, 2023-03-23, 2023-03-31, 2023-04-10, 2023-04-15, 2023-04-21, 2023-04-28, 2023-05-06, 2023-05-12, 2023-05-20, 2023-05-26, 2023-06-03, 2023-06-09, 2023-06-16, 2023-06-24, 2023-06-30, 2023-07-07, 2023-08-08, 2023-08-11, 2023-08-22, 2023-08-26, 2023-09-01, 2023-09-09, 2023-09-16, 2023-09-23, 2023-09-29, 2023-10-09, 2023-10-17, 2023-10-20, 2023-10-27, 2023-11-03, 2023-11-11, 2023-11-17, 2023-11-27, 2023-12-02, 2023-12-07, 2023-12-18, 2023-12-22, 2023-12-29, 2024-01-10, 2024-01-13, 2024-01-19, 2024-01-27, 2024-02-01, 2024-02-14, 2024-02-20, 2024-02-24, 2024-03-05, 2024-03-12, 2024-03-18, 2024-03-22, 2024-04-02, 2024-04-09, 2024-04-13, 2024-04-20, 2024-04-26, 2024-05-02, 2024-05-11, 2024-05-18, 2024-05-25, 2024-06-04, 2024-06-11, 2024-06-19, 2024-06-22, 2024-06-29, 2024-07-09, 2024-07-11, 2024-07-19, 2024-07-27, 2024-08-01, 2024-08-08, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-23, 2024-11-30, 2024-12-06, 2024-12-13, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-04, 2025-04-11, 2025-04-24, 2025-04-29, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-19, 2025-06-26, 2025-07-03, 2025-07-10, 2025-07-17, 2025-07-25, 2025-07-31, 2025-08-08, 2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-25, 2025-10-02, 2025-10-09, 2025-10-17, 2025-10-23, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-11, 2025-11-20, 2025-11-28, 2025-12-04, 2025-12-09, 2025-12-19, 2025-12-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2023-02-13, 2023-02-16, 2023-02-24, 2023-02-27, 2023-03-06, 2023-03-13, 2023-03-22, 2023-03-27, 2023-04-03, 2023-04-10, 2023-04-17, 2023-04-24, 2023-05-02, 2023-05-08, 2023-05-15, 2023-05-23, 2023-05-29, 2023-06-03, 2023-06-05, 2023-06-13, 2023-06-20, 2023-06-26, 2023-07-04, 2023-07-13, 2023-08-09, 2023-08-14, 2023-08-24, 2023-08-28, 2023-09-04, 2023-09-12, 2023-09-19, 2023-09-26, 2023-10-02, 2023-10-10, 2023-10-19, 2023-10-24, 2023-10-31, 2023-11-08, 2023-11-16, 2023-11-20, 2023-11-28, 2023-12-05, 2023-12-11, 2023-12-19, 2023-12-26, 2024-01-02, 2024-01-10, 2024-01-16, 2024-01-24, 2024-01-30, 2024-02-06, 2024-02-14, 2024-02-20, 2024-02-27, 2024-03-05, 2024-03-12, 2024-03-19, 2024-03-26, 2024-04-02, 2024-04-09, 2024-04-16, 2024-04-26, 2024-04-30, 2024-05-07, 2024-05-18, 2024-05-21, 2024-05-28, 2024-06-04, 2024-06-11, 2024-06-22, 2024-06-25, 2024-07-09, 2024-07-16, 2024-07-23, 2024-07-30, 2024-08-06, 2024-08-10, 2024-08-17, 2024-08-24, 2024-08-31, 2024-09-07, 2024-09-14, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-15, 2024-10-19, 2024-10-25, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2025-01-02, 2025-01-11, 2025-01-17, 2025-01-25, 2025-01-31, 2025-02-07, 2025-02-15, 2025-02-21, 2025-02-28, 2025-03-09, 2025-03-14, 2025-03-21, 2025-03-29, 2025-04-05, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-10, 2025-05-16, 2025-05-24, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-28, 2025-07-05, 2025-07-11, 2025-07-18, 2025-07-25, 2025-08-02, 2025-08-08, 2025-08-16, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-20, 2025-09-27, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-29, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-12, 2025-12-20, 2026-01-23, 2026-01-30, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1199,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2023-08-01, 2023-08-28, 2023-10-03, 2023-11-29, 2024-01-25, 2024-01-31, 2024-02-01, 2024-02-08, 2024-02-15, 2024-02-22, 2024-02-29, 2024-03-07, 2024-03-14, 2024-03-20, 2024-04-04, 2024-04-11, 2024-04-18, 2024-04-25, 2024-05-02, 2024-05-09, 2024-05-16, 2024-05-23, 2024-05-30, 2024-06-06, 2024-06-13, 2024-06-20, 2024-06-27, 2024-07-04, 2024-07-11, 2024-07-18, 2024-07-25, 2024-08-01, 2024-08-08, 2024-08-15, 2024-08-22, 2024-08-29, 2024-09-05, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-04, 2024-10-10, 2024-10-18, 2024-10-25, 2024-11-01, 2024-11-08, 2024-11-15, 2024-11-22, 2024-11-29, 2024-12-06, 2024-12-13, 2024-12-20, 2024-12-27, 2025-01-03, 2025-01-10, 2025-01-17, 2025-01-24, 2025-01-31, 2025-02-07, 2025-02-14, 2025-02-21, 2025-02-28, 2025-03-07, 2025-03-14, 2025-03-21, 2025-03-28, 2025-04-04, 2025-04-11, 2025-04-25, 2025-05-02, 2025-05-09, 2025-05-16, 2025-05-23, 2025-05-30, 2025-06-06, 2025-06-13, 2025-06-20, 2025-06-27, 2025-07-04, 2025-07-10, 2025-07-18, 2025-07-25, 2025-08-01, 2025-08-08, 2025-08-15, 2025-08-22, 2025-08-29, 2025-09-05, 2025-09-12, 2025-09-19, 2025-09-26, 2025-10-03, 2025-10-10, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-14, 2025-11-21, 2025-11-28, 2025-12-05, 2025-12-12, 2026-01-16, 2026-01-19, 2026-01-20, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2023-08-28, 2023-10-03, 2024-01-25, 2024-01-31, 2024-02-02, 2024-02-09, 2024-02-16, 2024-02-22, 2024-03-02, 2024-03-12, 2024-03-15, 2024-03-20, 2024-03-22, 2024-04-11, 2024-04-12, 2024-04-19, 2024-04-26, 2024-05-03, 2024-05-10, 2024-05-17, 2024-05-24, 2024-05-31, 2024-06-07, 2024-06-14, 2024-06-22, 2024-06-28, 2024-07-05, 2024-07-12, 2024-07-19, 2024-07-26, 2024-08-02, 2024-08-09, 2024-08-16, 2024-08-23, 2024-08-30, 2024-09-06, 2024-09-13, 2024-09-21, 2024-09-28, 2024-10-05, 2024-10-12, 2024-10-19, 2024-10-26, 2024-11-02, 2024-11-09, 2024-11-16, 2024-11-23, 2024-11-30, 2024-12-07, 2024-12-14, 2024-12-21, 2024-12-28, 2025-01-04, 2025-01-11, 2025-01-18, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-03-05, 2025-03-08, 2025-03-15, 2025-03-22, 2025-03-29, 2025-04-05, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-10, 2025-05-17, 2025-05-24, 2025-05-31, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-13, 2025-09-20, 2025-09-27, 2025-10-04, 2025-10-11, 2025-10-18, 2025-10-25, 2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29, 2025-12-06, 2025-12-13, 2026-01-17, 2026-01-20, 2026-01-24, 2026-01-31, 2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28, 2026-03-07, 2026-03-14</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1216,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2023-07-31, 2023-08-29, 2023-10-11, 2023-11-30, 2024-04-25, 2024-05-23, 2024-08-28, 2024-09-04, 2024-09-11, 2024-09-18, 2024-09-26, 2024-10-03, 2024-10-10, 2024-10-17, 2024-10-24, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-15, 2025-02-22, 2025-02-28, 2025-03-08, 2025-03-15, 2025-03-20, 2025-03-29, 2025-04-07, 2025-04-12, 2025-04-26, 2025-05-03, 2025-05-09, 2025-05-17, 2025-05-22, 2025-05-30, 2025-06-02, 2025-06-12, 2025-06-21, 2025-06-28, 2025-07-03, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-08, 2025-08-14, 2025-08-23, 2025-08-28, 2025-09-06, 2025-09-11, 2025-09-19, 2025-09-30, 2025-10-04, 2025-10-11, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-21, 2025-11-27, 2025-11-29, 2025-12-13, 2026-01-15, 2026-01-16, 2026-01-23, 2026-01-29, 2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-13, 2026-03-19</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2023-10-11, 2024-04-25, 2024-05-23, 2024-08-28, 2024-08-29, 2024-09-06, 2024-09-12, 2024-09-19, 2024-09-26, 2024-10-03, 2024-10-11, 2024-10-18, 2024-10-27, 2024-11-02, 2024-11-08, 2024-11-25, 2024-11-29, 2024-12-07, 2024-12-14, 2024-12-20, 2025-01-19, 2025-01-25, 2025-02-01, 2025-02-08, 2025-02-16, 2025-02-22, 2025-03-08, 2025-03-18, 2025-03-22, 2025-03-29, 2025-04-07, 2025-04-13, 2025-04-30, 2025-05-08, 2025-05-12, 2025-05-21, 2025-05-29, 2025-06-01, 2025-06-07, 2025-06-14, 2025-06-21, 2025-06-28, 2025-07-05, 2025-07-12, 2025-07-19, 2025-07-26, 2025-08-02, 2025-08-09, 2025-08-16, 2025-08-23, 2025-08-30, 2025-09-06, 2025-09-12, 2025-09-19, 2025-10-01, 2025-10-04, 2025-10-11, 2025-10-17, 2025-10-24, 2025-10-31, 2025-11-07, 2025-11-15, 2025-11-21, 2025-11-29, 2025-12-06, 2025-12-19, 2026-01-16, 2026-01-23, 2026-01-30, 2026-02-05, 2026-02-13, 2026-02-21, 2026-02-27, 2026-03-06, 2026-03-13</t>
+          <t>2026-02-05, 2026-02-13, 2026-02-21, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1233,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-08-14, 2025-08-21, 2025-08-28, 2025-09-05, 2025-09-11, 2025-09-18, 2025-09-25, 2025-10-03, 2025-10-09, 2025-10-16, 2025-10-23, 2025-10-30, 2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27, 2025-12-04, 2025-12-11, 2025-12-18, 2026-01-08, 2026-01-15, 2026-01-22, 2026-01-29, 2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26, 2026-03-05, 2026-03-12</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025-08-15, 2025-08-22, 2025-09-02, 2025-09-05, 2025-09-13, 2025-09-19, 2025-09-26, 2025-10-04, 2025-10-11, 2025-10-23, 2025-10-28, 2025-10-31, 2025-11-11, 2025-11-14, 2025-11-21, 2025-12-04, 2025-12-09, 2025-12-12, 2025-12-19, 2026-01-09, 2026-01-19, 2026-01-23, 2026-01-30, 2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28, 2026-03-07, 2026-03-13</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-28</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,115 +446,196 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMARETTO</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C DEL PARQUE TAYRONA APTOS</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+          <t>DIMARO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-11, 2026-03-20, 2026-03-31</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DIMARO</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+          <t>GENOVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-14</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GENOVA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>PARKSIDE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-09, 2026-03-18, 2026-03-21</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PARKSIDE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>PUERTA DORADA ARRECIFE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PUERTA DORADA ARRECIFE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+          <t>PUERTA DORADA MARISMA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PUERTA DORADA MARISMA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+          <t>PUERTA DORADA NATURA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-13, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PUERTA DORADA NATURA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+          <t>RIVERBLUE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RIVERBLUE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+          <t>PUERTA DORADA CRISTALINA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LOTE SEVILLA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-03-12, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-18, 2026-03-31</t>
+          <t>2026-03-06, 2026-03-10, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-20, 2026-03-31</t>
+          <t>2026-03-09, 2026-03-11, 2026-03-20, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-06, 2026-03-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-18</t>
+          <t>2026-03-09, 2026-03-18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-18, 2026-03-21</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-18, 2026-03-21</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-21, 2026-03-30</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-13, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-06, 2026-03-20, 2026-03-30</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-30</t>
         </is>
       </c>
     </row>
